--- a/research/traditional_assets/database/data/nigeria/nigeria_computer_services.xlsx
+++ b/research/traditional_assets/database/data/nigeria/nigeria_computer_services.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1881157153423537</v>
+        <v>0.1875828681963266</v>
       </c>
       <c r="C2">
-        <v>14.86841259691816</v>
+        <v>14.76413988780375</v>
       </c>
       <c r="D2">
-        <v>11.68841259691816</v>
+        <v>11.73233988780375</v>
       </c>
       <c r="E2">
-        <v>-2.22</v>
+        <v>-2.0718</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>0.1482</v>
       </c>
       <c r="G2">
         <v>3.18</v>
@@ -1445,28 +1445,28 @@
         <v>2.061</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.00745446</v>
       </c>
       <c r="N2">
-        <v>2.061</v>
+        <v>2.05354554</v>
       </c>
       <c r="O2">
-        <v>0.6183000000000001</v>
+        <v>0.6160636620000001</v>
       </c>
       <c r="P2">
-        <v>1.4427</v>
+        <v>1.437481878</v>
       </c>
       <c r="Q2">
-        <v>1.6017</v>
+        <v>1.596481878</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1881157153423537</v>
+        <v>0.1891219880770976</v>
       </c>
       <c r="T2">
-        <v>0.9922881498763958</v>
+        <v>0.9993043287139056</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>276.4787791469805</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1875828681963266</v>
+        <v>0.1870500210502995</v>
       </c>
       <c r="C3">
-        <v>14.76413988780375</v>
+        <v>14.66019859855616</v>
       </c>
       <c r="D3">
-        <v>11.73233988780375</v>
+        <v>11.77659859855616</v>
       </c>
       <c r="E3">
-        <v>-2.0718</v>
+        <v>-1.9236</v>
       </c>
       <c r="F3">
-        <v>0.1482</v>
+        <v>0.2964</v>
       </c>
       <c r="G3">
         <v>3.18</v>
@@ -1527,28 +1527,28 @@
         <v>2.061</v>
       </c>
       <c r="M3">
-        <v>0.00745446</v>
+        <v>0.01490892</v>
       </c>
       <c r="N3">
-        <v>2.05354554</v>
+        <v>2.046091080000001</v>
       </c>
       <c r="O3">
-        <v>0.6160636620000001</v>
+        <v>0.6138273240000002</v>
       </c>
       <c r="P3">
-        <v>1.437481878</v>
+        <v>1.432263756</v>
       </c>
       <c r="Q3">
-        <v>1.596481878</v>
+        <v>1.591263756</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1891219880770976</v>
+        <v>0.1901487969901016</v>
       </c>
       <c r="T3">
-        <v>0.9993043287139056</v>
+        <v>1.00646369487463</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>276.4787791469805</v>
+        <v>138.2393895734903</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1870500210502995</v>
+        <v>0.1865171739042725</v>
       </c>
       <c r="C4">
-        <v>14.66019859855616</v>
+        <v>14.55659249409172</v>
       </c>
       <c r="D4">
-        <v>11.77659859855616</v>
+        <v>11.82119249409172</v>
       </c>
       <c r="E4">
-        <v>-1.9236</v>
+        <v>-1.7754</v>
       </c>
       <c r="F4">
-        <v>0.2964</v>
+        <v>0.4446</v>
       </c>
       <c r="G4">
         <v>3.18</v>
@@ -1609,28 +1609,28 @@
         <v>2.061</v>
       </c>
       <c r="M4">
-        <v>0.01490892</v>
+        <v>0.02236338</v>
       </c>
       <c r="N4">
-        <v>2.046091080000001</v>
+        <v>2.038636620000001</v>
       </c>
       <c r="O4">
-        <v>0.6138273240000002</v>
+        <v>0.6115909860000002</v>
       </c>
       <c r="P4">
-        <v>1.432263756</v>
+        <v>1.427045634</v>
       </c>
       <c r="Q4">
-        <v>1.591263756</v>
+        <v>1.586045634</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1901487969901016</v>
+        <v>0.1911967772208994</v>
       </c>
       <c r="T4">
-        <v>1.00646369487463</v>
+        <v>1.013770676832483</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>138.2393895734903</v>
+        <v>92.15959304899351</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1865171739042725</v>
+        <v>0.1859843267582454</v>
       </c>
       <c r="C5">
-        <v>14.55659249409172</v>
+        <v>14.4533253965693</v>
       </c>
       <c r="D5">
-        <v>11.82119249409172</v>
+        <v>11.8661253965693</v>
       </c>
       <c r="E5">
-        <v>-1.7754</v>
+        <v>-1.6272</v>
       </c>
       <c r="F5">
-        <v>0.4446</v>
+        <v>0.5928</v>
       </c>
       <c r="G5">
         <v>3.18</v>
@@ -1691,28 +1691,28 @@
         <v>2.061</v>
       </c>
       <c r="M5">
-        <v>0.02236338</v>
+        <v>0.02981784</v>
       </c>
       <c r="N5">
-        <v>2.038636620000001</v>
+        <v>2.03118216</v>
       </c>
       <c r="O5">
-        <v>0.6115909860000002</v>
+        <v>0.6093546480000001</v>
       </c>
       <c r="P5">
-        <v>1.427045634</v>
+        <v>1.421827512</v>
       </c>
       <c r="Q5">
-        <v>1.586045634</v>
+        <v>1.580827512</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1911967772208994</v>
+        <v>0.1922665903731723</v>
       </c>
       <c r="T5">
-        <v>1.013770676832483</v>
+        <v>1.021229887581124</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>92.15959304899351</v>
+        <v>69.11969478674513</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.1859843267582454</v>
+        <v>0.1854514796122183</v>
       </c>
       <c r="C6">
-        <v>14.4533253965693</v>
+        <v>14.35040118648229</v>
       </c>
       <c r="D6">
-        <v>11.8661253965693</v>
+        <v>11.91140118648229</v>
       </c>
       <c r="E6">
-        <v>-1.6272</v>
+        <v>-1.479</v>
       </c>
       <c r="F6">
-        <v>0.5928</v>
+        <v>0.7410000000000001</v>
       </c>
       <c r="G6">
         <v>3.18</v>
@@ -1773,28 +1773,28 @@
         <v>2.061</v>
       </c>
       <c r="M6">
-        <v>0.02981784</v>
+        <v>0.0372723</v>
       </c>
       <c r="N6">
-        <v>2.03118216</v>
+        <v>2.0237277</v>
       </c>
       <c r="O6">
-        <v>0.6093546480000001</v>
+        <v>0.60711831</v>
       </c>
       <c r="P6">
-        <v>1.421827512</v>
+        <v>1.41660939</v>
       </c>
       <c r="Q6">
-        <v>1.580827512</v>
+        <v>1.57560939</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1922665903731723</v>
+        <v>0.1933589259075983</v>
       </c>
       <c r="T6">
-        <v>1.021229887581124</v>
+        <v>1.028846134345526</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>69.11969478674513</v>
+        <v>55.2957558293961</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1854514796122183</v>
+        <v>0.1849186324661913</v>
       </c>
       <c r="C7">
-        <v>14.35040118648229</v>
+        <v>14.24782380377579</v>
       </c>
       <c r="D7">
-        <v>11.91140118648229</v>
+        <v>11.95702380377579</v>
       </c>
       <c r="E7">
-        <v>-1.479</v>
+        <v>-1.3308</v>
       </c>
       <c r="F7">
-        <v>0.7410000000000001</v>
+        <v>0.8892000000000001</v>
       </c>
       <c r="G7">
         <v>3.18</v>
@@ -1855,28 +1855,28 @@
         <v>2.061</v>
       </c>
       <c r="M7">
-        <v>0.0372723</v>
+        <v>0.04472676</v>
       </c>
       <c r="N7">
-        <v>2.0237277</v>
+        <v>2.01627324</v>
       </c>
       <c r="O7">
-        <v>0.60711831</v>
+        <v>0.604881972</v>
       </c>
       <c r="P7">
-        <v>1.41660939</v>
+        <v>1.411391268</v>
       </c>
       <c r="Q7">
-        <v>1.57560939</v>
+        <v>1.570391268</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1933589259075983</v>
+        <v>0.1944745026236077</v>
       </c>
       <c r="T7">
-        <v>1.028846134345526</v>
+        <v>1.036624428913426</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>55.2957558293961</v>
+        <v>46.07979652449675</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1849186324661913</v>
+        <v>0.1843857853201642</v>
       </c>
       <c r="C8">
-        <v>14.24782380377579</v>
+        <v>14.14559724898953</v>
       </c>
       <c r="D8">
-        <v>11.95702380377579</v>
+        <v>12.00299724898953</v>
       </c>
       <c r="E8">
-        <v>-1.3308</v>
+        <v>-1.1826</v>
       </c>
       <c r="F8">
-        <v>0.8892</v>
+        <v>1.0374</v>
       </c>
       <c r="G8">
         <v>3.18</v>
@@ -1937,28 +1937,28 @@
         <v>2.061</v>
       </c>
       <c r="M8">
-        <v>0.04472676</v>
+        <v>0.05218121999999999</v>
       </c>
       <c r="N8">
-        <v>2.01627324</v>
+        <v>2.00881878</v>
       </c>
       <c r="O8">
-        <v>0.604881972</v>
+        <v>0.602645634</v>
       </c>
       <c r="P8">
-        <v>1.411391268</v>
+        <v>1.406173146</v>
       </c>
       <c r="Q8">
-        <v>1.570391268</v>
+        <v>1.565173146</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1944745026236077</v>
+        <v>0.1956140702367357</v>
       </c>
       <c r="T8">
-        <v>1.036624428913426</v>
+        <v>1.044569998633324</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>46.07979652449676</v>
+        <v>39.49696844956865</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1843857853201643</v>
+        <v>0.1838529381741372</v>
       </c>
       <c r="C9">
-        <v>14.14559724898953</v>
+        <v>14.04372558442725</v>
       </c>
       <c r="D9">
-        <v>12.00299724898953</v>
+        <v>12.04932558442725</v>
       </c>
       <c r="E9">
-        <v>-1.1826</v>
+        <v>-1.0344</v>
       </c>
       <c r="F9">
-        <v>1.0374</v>
+        <v>1.1856</v>
       </c>
       <c r="G9">
         <v>3.18</v>
@@ -2019,28 +2019,28 @@
         <v>2.061</v>
       </c>
       <c r="M9">
-        <v>0.05218122</v>
+        <v>0.05963568</v>
       </c>
       <c r="N9">
-        <v>2.00881878</v>
+        <v>2.00136432</v>
       </c>
       <c r="O9">
-        <v>0.602645634</v>
+        <v>0.6004092960000001</v>
       </c>
       <c r="P9">
-        <v>1.406173146</v>
+        <v>1.400955024</v>
       </c>
       <c r="Q9">
-        <v>1.565173146</v>
+        <v>1.559955024</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1956140702367357</v>
+        <v>0.1967784110588448</v>
       </c>
       <c r="T9">
-        <v>1.044569998633324</v>
+        <v>1.052688298129742</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>39.49696844956865</v>
+        <v>34.55984739337256</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1838529381741372</v>
+        <v>0.1833200910281101</v>
       </c>
       <c r="C10">
-        <v>14.04372558442725</v>
+        <v>13.94221293535331</v>
       </c>
       <c r="D10">
-        <v>12.04932558442725</v>
+        <v>12.09601293535331</v>
       </c>
       <c r="E10">
-        <v>-1.0344</v>
+        <v>-0.8862000000000003</v>
       </c>
       <c r="F10">
-        <v>1.1856</v>
+        <v>1.3338</v>
       </c>
       <c r="G10">
         <v>3.18</v>
@@ -2101,28 +2101,28 @@
         <v>2.061</v>
       </c>
       <c r="M10">
-        <v>0.05963568</v>
+        <v>0.06709013999999999</v>
       </c>
       <c r="N10">
-        <v>2.00136432</v>
+        <v>1.99390986</v>
       </c>
       <c r="O10">
-        <v>0.6004092960000001</v>
+        <v>0.5981729580000001</v>
       </c>
       <c r="P10">
-        <v>1.400955024</v>
+        <v>1.395736902</v>
       </c>
       <c r="Q10">
-        <v>1.559955024</v>
+        <v>1.554736902</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1967784110588448</v>
+        <v>0.197968341789132</v>
       </c>
       <c r="T10">
-        <v>1.052688298129742</v>
+        <v>1.060985021790916</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>34.55984739337256</v>
+        <v>30.71986434966451</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.1833200910281101</v>
+        <v>0.1827872438820831</v>
       </c>
       <c r="C11">
-        <v>13.94221293535331</v>
+        <v>13.84106349121716</v>
       </c>
       <c r="D11">
-        <v>12.09601293535331</v>
+        <v>12.14306349121716</v>
       </c>
       <c r="E11">
-        <v>-0.8862000000000003</v>
+        <v>-0.7380000000000002</v>
       </c>
       <c r="F11">
-        <v>1.3338</v>
+        <v>1.482</v>
       </c>
       <c r="G11">
         <v>3.18</v>
@@ -2183,28 +2183,28 @@
         <v>2.061</v>
       </c>
       <c r="M11">
-        <v>0.06709013999999999</v>
+        <v>0.07454459999999999</v>
       </c>
       <c r="N11">
-        <v>1.99390986</v>
+        <v>1.9864554</v>
       </c>
       <c r="O11">
-        <v>0.5981729580000001</v>
+        <v>0.59593662</v>
       </c>
       <c r="P11">
-        <v>1.395736902</v>
+        <v>1.39051878</v>
       </c>
       <c r="Q11">
-        <v>1.554736902</v>
+        <v>1.54951878</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.197968341789132</v>
+        <v>0.1991847154245367</v>
       </c>
       <c r="T11">
-        <v>1.060985021790916</v>
+        <v>1.069466117089004</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2221,7 +2221,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>30.71986434966451</v>
+        <v>27.64787791469805</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1827872438820831</v>
+        <v>0.182254396736056</v>
       </c>
       <c r="C12">
-        <v>13.84106349121716</v>
+        <v>13.74028150690658</v>
       </c>
       <c r="D12">
-        <v>12.14306349121716</v>
+        <v>12.19048150690658</v>
       </c>
       <c r="E12">
-        <v>-0.738</v>
+        <v>-0.5898000000000001</v>
       </c>
       <c r="F12">
-        <v>1.482</v>
+        <v>1.6302</v>
       </c>
       <c r="G12">
         <v>3.18</v>
@@ -2265,28 +2265,28 @@
         <v>2.061</v>
       </c>
       <c r="M12">
-        <v>0.0745446</v>
+        <v>0.08199906</v>
       </c>
       <c r="N12">
-        <v>1.9864554</v>
+        <v>1.97900094</v>
       </c>
       <c r="O12">
-        <v>0.59593662</v>
+        <v>0.5937002820000001</v>
       </c>
       <c r="P12">
-        <v>1.39051878</v>
+        <v>1.385300658</v>
       </c>
       <c r="Q12">
-        <v>1.54951878</v>
+        <v>1.544300658</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1991847154245367</v>
+        <v>0.2004284232989393</v>
       </c>
       <c r="T12">
-        <v>1.069466117089004</v>
+        <v>1.078137798798286</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>27.64787791469805</v>
+        <v>25.13443446790732</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.182254396736056</v>
+        <v>0.181721549590029</v>
       </c>
       <c r="C13">
-        <v>13.74028150690658</v>
+        <v>13.63987130403032</v>
       </c>
       <c r="D13">
-        <v>12.19048150690658</v>
+        <v>12.23827130403032</v>
       </c>
       <c r="E13">
-        <v>-0.5898000000000001</v>
+        <v>-0.4416000000000002</v>
       </c>
       <c r="F13">
-        <v>1.6302</v>
+        <v>1.7784</v>
       </c>
       <c r="G13">
         <v>3.18</v>
@@ -2347,28 +2347,28 @@
         <v>2.061</v>
       </c>
       <c r="M13">
-        <v>0.08199906</v>
+        <v>0.08945351999999999</v>
       </c>
       <c r="N13">
-        <v>1.97900094</v>
+        <v>1.97154648</v>
       </c>
       <c r="O13">
-        <v>0.5937002820000001</v>
+        <v>0.5914639440000001</v>
       </c>
       <c r="P13">
-        <v>1.385300658</v>
+        <v>1.380082536</v>
       </c>
       <c r="Q13">
-        <v>1.544300658</v>
+        <v>1.539082536</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.2004284232989393</v>
+        <v>0.2017003972613965</v>
       </c>
       <c r="T13">
-        <v>1.078137798798286</v>
+        <v>1.087006564182779</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>25.13443446790732</v>
+        <v>23.03989826224838</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.181721549590029</v>
+        <v>0.1811887024440019</v>
       </c>
       <c r="C14">
-        <v>13.63987130403032</v>
+        <v>13.53983727223106</v>
       </c>
       <c r="D14">
-        <v>12.23827130403032</v>
+        <v>12.28643727223106</v>
       </c>
       <c r="E14">
-        <v>-0.4416000000000002</v>
+        <v>-0.2934000000000001</v>
       </c>
       <c r="F14">
-        <v>1.7784</v>
+        <v>1.9266</v>
       </c>
       <c r="G14">
         <v>3.18</v>
@@ -2429,28 +2429,28 @@
         <v>2.061</v>
       </c>
       <c r="M14">
-        <v>0.08945351999999999</v>
+        <v>0.09690798</v>
       </c>
       <c r="N14">
-        <v>1.97154648</v>
+        <v>1.96409202</v>
       </c>
       <c r="O14">
-        <v>0.5914639440000001</v>
+        <v>0.589227606</v>
       </c>
       <c r="P14">
-        <v>1.380082536</v>
+        <v>1.374864414</v>
       </c>
       <c r="Q14">
-        <v>1.539082536</v>
+        <v>1.533864414</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.2017003972613965</v>
+        <v>0.2030016120045999</v>
       </c>
       <c r="T14">
-        <v>1.087006564182779</v>
+        <v>1.096079209231283</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2467,7 +2467,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>23.03989826224838</v>
+        <v>21.26759839592158</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1811887024440019</v>
+        <v>0.1806558552979748</v>
       </c>
       <c r="C15">
-        <v>13.53983727223106</v>
+        <v>13.44018387052954</v>
       </c>
       <c r="D15">
-        <v>12.28643727223106</v>
+        <v>12.33498387052954</v>
       </c>
       <c r="E15">
-        <v>-0.2934000000000001</v>
+        <v>-0.1452</v>
       </c>
       <c r="F15">
-        <v>1.9266</v>
+        <v>2.0748</v>
       </c>
       <c r="G15">
         <v>3.18</v>
@@ -2511,28 +2511,28 @@
         <v>2.061</v>
       </c>
       <c r="M15">
-        <v>0.09690798</v>
+        <v>0.10436244</v>
       </c>
       <c r="N15">
-        <v>1.96409202</v>
+        <v>1.95663756</v>
       </c>
       <c r="O15">
-        <v>0.589227606</v>
+        <v>0.5869912680000001</v>
       </c>
       <c r="P15">
-        <v>1.374864414</v>
+        <v>1.369646292</v>
       </c>
       <c r="Q15">
-        <v>1.533864414</v>
+        <v>1.528646292</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.2030016120045999</v>
+        <v>0.2043330875557847</v>
       </c>
       <c r="T15">
-        <v>1.096079209231283</v>
+        <v>1.105362846025101</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>21.26759839592158</v>
+        <v>19.74848422478432</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1806558552979748</v>
+        <v>0.1801230081519477</v>
       </c>
       <c r="C16">
-        <v>13.44018387052954</v>
+        <v>13.34091562870061</v>
       </c>
       <c r="D16">
-        <v>12.33498387052954</v>
+        <v>12.38391562870061</v>
       </c>
       <c r="E16">
-        <v>-0.1452</v>
+        <v>0.003000000000000114</v>
       </c>
       <c r="F16">
-        <v>2.0748</v>
+        <v>2.223</v>
       </c>
       <c r="G16">
         <v>3.18</v>
@@ -2593,28 +2593,28 @@
         <v>2.061</v>
       </c>
       <c r="M16">
-        <v>0.10436244</v>
+        <v>0.1118169</v>
       </c>
       <c r="N16">
-        <v>1.95663756</v>
+        <v>1.9491831</v>
       </c>
       <c r="O16">
-        <v>0.5869912680000001</v>
+        <v>0.5847549300000001</v>
       </c>
       <c r="P16">
-        <v>1.369646292</v>
+        <v>1.36442817</v>
       </c>
       <c r="Q16">
-        <v>1.528646292</v>
+        <v>1.52342817</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.2043330875557847</v>
+        <v>0.2056958919434679</v>
       </c>
       <c r="T16">
-        <v>1.105362846025101</v>
+        <v>1.114864921331715</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>19.74848422478432</v>
+        <v>18.4319186097987</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1801230081519477</v>
+        <v>0.1795901610059207</v>
       </c>
       <c r="C17">
-        <v>13.34091562870061</v>
+        <v>13.24203714868219</v>
       </c>
       <c r="D17">
-        <v>12.38391562870061</v>
+        <v>12.43323714868219</v>
       </c>
       <c r="E17">
-        <v>0.00299999999999967</v>
+        <v>0.1511999999999998</v>
       </c>
       <c r="F17">
-        <v>2.223</v>
+        <v>2.3712</v>
       </c>
       <c r="G17">
         <v>3.18</v>
@@ -2675,28 +2675,28 @@
         <v>2.061</v>
       </c>
       <c r="M17">
-        <v>0.1118169</v>
+        <v>0.11927136</v>
       </c>
       <c r="N17">
-        <v>1.9491831</v>
+        <v>1.94172864</v>
       </c>
       <c r="O17">
-        <v>0.5847549300000001</v>
+        <v>0.5825185920000001</v>
       </c>
       <c r="P17">
-        <v>1.36442817</v>
+        <v>1.359210048</v>
       </c>
       <c r="Q17">
-        <v>1.52342817</v>
+        <v>1.518210048</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.2056958919434679</v>
+        <v>0.2070911440546675</v>
       </c>
       <c r="T17">
-        <v>1.114864921331715</v>
+        <v>1.124593236526582</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2713,7 +2713,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>18.4319186097987</v>
+        <v>17.27992369668628</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1795901610059207</v>
+        <v>0.1790573138598937</v>
       </c>
       <c r="C18">
-        <v>13.24203714868219</v>
+        <v>13.14355310601807</v>
       </c>
       <c r="D18">
-        <v>12.43323714868219</v>
+        <v>12.48295310601807</v>
       </c>
       <c r="E18">
-        <v>0.1511999999999998</v>
+        <v>0.2993999999999999</v>
       </c>
       <c r="F18">
-        <v>2.3712</v>
+        <v>2.5194</v>
       </c>
       <c r="G18">
         <v>3.18</v>
@@ -2757,28 +2757,28 @@
         <v>2.061</v>
       </c>
       <c r="M18">
-        <v>0.11927136</v>
+        <v>0.12672582</v>
       </c>
       <c r="N18">
-        <v>1.94172864</v>
+        <v>1.934274180000001</v>
       </c>
       <c r="O18">
-        <v>0.5825185920000001</v>
+        <v>0.5802822540000001</v>
       </c>
       <c r="P18">
-        <v>1.359210048</v>
+        <v>1.353991926</v>
       </c>
       <c r="Q18">
-        <v>1.518210048</v>
+        <v>1.512991926</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.2070911440546675</v>
+        <v>0.2085200166986671</v>
       </c>
       <c r="T18">
-        <v>1.124593236526582</v>
+        <v>1.13455596895506</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>17.27992369668628</v>
+        <v>16.26345759688121</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1790573138598937</v>
+        <v>0.1785244667138665</v>
       </c>
       <c r="C19">
-        <v>13.14355310601807</v>
+        <v>13.04546825133542</v>
       </c>
       <c r="D19">
-        <v>12.48295310601807</v>
+        <v>12.53306825133542</v>
       </c>
       <c r="E19">
-        <v>0.2993999999999999</v>
+        <v>0.4476</v>
       </c>
       <c r="F19">
-        <v>2.5194</v>
+        <v>2.6676</v>
       </c>
       <c r="G19">
         <v>3.18</v>
@@ -2839,28 +2839,28 @@
         <v>2.061</v>
       </c>
       <c r="M19">
-        <v>0.12672582</v>
+        <v>0.13418028</v>
       </c>
       <c r="N19">
-        <v>1.934274180000001</v>
+        <v>1.92681972</v>
       </c>
       <c r="O19">
-        <v>0.5802822540000001</v>
+        <v>0.5780459160000001</v>
       </c>
       <c r="P19">
-        <v>1.353991926</v>
+        <v>1.348773804</v>
       </c>
       <c r="Q19">
-        <v>1.512991926</v>
+        <v>1.507773804</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.2085200166986671</v>
+        <v>0.2099837398949592</v>
       </c>
       <c r="T19">
-        <v>1.13455596895506</v>
+        <v>1.144761694857403</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>16.26345759688121</v>
+        <v>15.35993217483225</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1785244667138666</v>
+        <v>0.1779916195678395</v>
       </c>
       <c r="C20">
-        <v>13.04546825133541</v>
+        <v>12.94778741185798</v>
       </c>
       <c r="D20">
-        <v>12.53306825133541</v>
+        <v>12.58358741185798</v>
       </c>
       <c r="E20">
-        <v>0.4475999999999996</v>
+        <v>0.5958000000000001</v>
       </c>
       <c r="F20">
-        <v>2.6676</v>
+        <v>2.8158</v>
       </c>
       <c r="G20">
         <v>3.18</v>
@@ -2921,28 +2921,28 @@
         <v>2.061</v>
       </c>
       <c r="M20">
-        <v>0.13418028</v>
+        <v>0.14163474</v>
       </c>
       <c r="N20">
-        <v>1.92681972</v>
+        <v>1.91936526</v>
       </c>
       <c r="O20">
-        <v>0.5780459160000001</v>
+        <v>0.5758095780000001</v>
       </c>
       <c r="P20">
-        <v>1.348773804</v>
+        <v>1.343555682</v>
       </c>
       <c r="Q20">
-        <v>1.507773804</v>
+        <v>1.502555682</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.2099837398949592</v>
+        <v>0.2114836044047401</v>
       </c>
       <c r="T20">
-        <v>1.144761694857403</v>
+        <v>1.155219413991903</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2959,7 +2959,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>15.35993217483225</v>
+        <v>14.55151469194634</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1779916195678395</v>
+        <v>0.1774587724218125</v>
       </c>
       <c r="C21">
-        <v>12.94778741185798</v>
+        <v>12.85051549295621</v>
       </c>
       <c r="D21">
-        <v>12.58358741185798</v>
+        <v>12.63451549295621</v>
       </c>
       <c r="E21">
-        <v>0.5958000000000001</v>
+        <v>0.7440000000000002</v>
       </c>
       <c r="F21">
-        <v>2.8158</v>
+        <v>2.964</v>
       </c>
       <c r="G21">
         <v>3.18</v>
@@ -3003,28 +3003,28 @@
         <v>2.061</v>
       </c>
       <c r="M21">
-        <v>0.14163474</v>
+        <v>0.1490892</v>
       </c>
       <c r="N21">
-        <v>1.91936526</v>
+        <v>1.9119108</v>
       </c>
       <c r="O21">
-        <v>0.5758095780000001</v>
+        <v>0.5735732400000001</v>
       </c>
       <c r="P21">
-        <v>1.343555682</v>
+        <v>1.33833756</v>
       </c>
       <c r="Q21">
-        <v>1.502555682</v>
+        <v>1.49733756</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.2114836044047401</v>
+        <v>0.2130209655272656</v>
       </c>
       <c r="T21">
-        <v>1.155219413991903</v>
+        <v>1.165938576104765</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>14.55151469194634</v>
+        <v>13.82393895734903</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1774587724218125</v>
+        <v>0.1769259252757854</v>
       </c>
       <c r="C22">
-        <v>12.85051549295621</v>
+        <v>12.75365747973492</v>
       </c>
       <c r="D22">
-        <v>12.63451549295621</v>
+        <v>12.68585747973492</v>
       </c>
       <c r="E22">
-        <v>0.7440000000000002</v>
+        <v>0.8922000000000003</v>
       </c>
       <c r="F22">
-        <v>2.964</v>
+        <v>3.112200000000001</v>
       </c>
       <c r="G22">
         <v>3.18</v>
@@ -3085,28 +3085,28 @@
         <v>2.061</v>
       </c>
       <c r="M22">
-        <v>0.1490892</v>
+        <v>0.15654366</v>
       </c>
       <c r="N22">
-        <v>1.9119108</v>
+        <v>1.90445634</v>
       </c>
       <c r="O22">
-        <v>0.5735732400000001</v>
+        <v>0.5713369020000001</v>
       </c>
       <c r="P22">
-        <v>1.33833756</v>
+        <v>1.333119438</v>
       </c>
       <c r="Q22">
-        <v>1.49733756</v>
+        <v>1.492119438</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.2130209655272656</v>
+        <v>0.2145972471845385</v>
       </c>
       <c r="T22">
-        <v>1.165938576104765</v>
+        <v>1.176929109410358</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>13.82393895734903</v>
+        <v>13.16565614985621</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.1769259252757854</v>
+        <v>0.1766240781297583</v>
       </c>
       <c r="C23">
-        <v>12.75365747973493</v>
+        <v>12.63472724360336</v>
       </c>
       <c r="D23">
-        <v>12.68585747973493</v>
+        <v>12.71512724360336</v>
       </c>
       <c r="E23">
-        <v>0.8921999999999999</v>
+        <v>1.0404</v>
       </c>
       <c r="F23">
-        <v>3.1122</v>
+        <v>3.2604</v>
       </c>
       <c r="G23">
         <v>3.18</v>
@@ -3167,45 +3167,45 @@
         <v>2.061</v>
       </c>
       <c r="M23">
-        <v>0.15654366</v>
+        <v>0.16888872</v>
       </c>
       <c r="N23">
-        <v>1.90445634</v>
+        <v>1.89211128</v>
       </c>
       <c r="O23">
-        <v>0.5713369020000001</v>
+        <v>0.5676333840000001</v>
       </c>
       <c r="P23">
-        <v>1.333119438</v>
+        <v>1.324477896</v>
       </c>
       <c r="Q23">
-        <v>1.492119438</v>
+        <v>1.483477896</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.2145972471845385</v>
+        <v>0.216213946320203</v>
       </c>
       <c r="T23">
-        <v>1.176929109410358</v>
+        <v>1.188201451262248</v>
       </c>
       <c r="U23">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V23">
         <v>0.3</v>
       </c>
       <c r="W23">
-        <v>0.03521</v>
+        <v>0.03625999999999999</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y23">
-        <v>13.16565614985621</v>
+        <v>12.20330167698589</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1766240781297583</v>
+        <v>0.1761017309837313</v>
       </c>
       <c r="C24">
-        <v>12.63472724360336</v>
+        <v>12.53749901793763</v>
       </c>
       <c r="D24">
-        <v>12.71512724360336</v>
+        <v>12.76609901793763</v>
       </c>
       <c r="E24">
-        <v>1.0404</v>
+        <v>1.1886</v>
       </c>
       <c r="F24">
-        <v>3.2604</v>
+        <v>3.4086</v>
       </c>
       <c r="G24">
         <v>3.18</v>
@@ -3249,28 +3249,28 @@
         <v>2.061</v>
       </c>
       <c r="M24">
-        <v>0.16888872</v>
+        <v>0.17656548</v>
       </c>
       <c r="N24">
-        <v>1.89211128</v>
+        <v>1.88443452</v>
       </c>
       <c r="O24">
-        <v>0.5676333840000001</v>
+        <v>0.565330356</v>
       </c>
       <c r="P24">
-        <v>1.324477896</v>
+        <v>1.319104164</v>
       </c>
       <c r="Q24">
-        <v>1.483477896</v>
+        <v>1.478104164</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.216213946320203</v>
+        <v>0.2178726376412094</v>
       </c>
       <c r="T24">
-        <v>1.188201451262248</v>
+        <v>1.199766581214188</v>
       </c>
       <c r="U24">
         <v>0.0518</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>12.20330167698589</v>
+        <v>11.67272334320389</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1761017309837313</v>
+        <v>0.1755793838377042</v>
       </c>
       <c r="C25">
-        <v>12.53749901793763</v>
+        <v>12.44068110337161</v>
       </c>
       <c r="D25">
-        <v>12.76609901793763</v>
+        <v>12.81748110337161</v>
       </c>
       <c r="E25">
-        <v>1.1886</v>
+        <v>1.3368</v>
       </c>
       <c r="F25">
-        <v>3.4086</v>
+        <v>3.5568</v>
       </c>
       <c r="G25">
         <v>3.18</v>
@@ -3331,28 +3331,28 @@
         <v>2.061</v>
       </c>
       <c r="M25">
-        <v>0.17656548</v>
+        <v>0.18424224</v>
       </c>
       <c r="N25">
-        <v>1.88443452</v>
+        <v>1.87675776</v>
       </c>
       <c r="O25">
-        <v>0.565330356</v>
+        <v>0.5630273280000001</v>
       </c>
       <c r="P25">
-        <v>1.319104164</v>
+        <v>1.313730432</v>
       </c>
       <c r="Q25">
-        <v>1.478104164</v>
+        <v>1.472730432</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.2178726376412094</v>
+        <v>0.2195749787338213</v>
       </c>
       <c r="T25">
-        <v>1.199766581214188</v>
+        <v>1.211636056691178</v>
       </c>
       <c r="U25">
         <v>0.0518</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>11.67272334320389</v>
+        <v>11.1863598705704</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1755793838377042</v>
+        <v>0.1750570366916772</v>
       </c>
       <c r="C26">
-        <v>12.44068110337161</v>
+        <v>12.3442784742921</v>
       </c>
       <c r="D26">
-        <v>12.81748110337161</v>
+        <v>12.8692784742921</v>
       </c>
       <c r="E26">
-        <v>1.3368</v>
+        <v>1.485</v>
       </c>
       <c r="F26">
-        <v>3.5568</v>
+        <v>3.705</v>
       </c>
       <c r="G26">
         <v>3.18</v>
@@ -3413,28 +3413,28 @@
         <v>2.061</v>
       </c>
       <c r="M26">
-        <v>0.18424224</v>
+        <v>0.191919</v>
       </c>
       <c r="N26">
-        <v>1.87675776</v>
+        <v>1.869081</v>
       </c>
       <c r="O26">
-        <v>0.5630273280000001</v>
+        <v>0.5607243000000001</v>
       </c>
       <c r="P26">
-        <v>1.313730432</v>
+        <v>1.3083567</v>
       </c>
       <c r="Q26">
-        <v>1.472730432</v>
+        <v>1.467356700000001</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.2195749787338213</v>
+        <v>0.2213227155889029</v>
       </c>
       <c r="T26">
-        <v>1.211636056691178</v>
+        <v>1.223822051514222</v>
       </c>
       <c r="U26">
         <v>0.0518</v>
@@ -3451,7 +3451,7 @@
         </is>
       </c>
       <c r="Y26">
-        <v>11.1863598705704</v>
+        <v>10.73890547574758</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1750570366916772</v>
+        <v>0.1745346895456501</v>
       </c>
       <c r="C27">
-        <v>12.3442784742921</v>
+        <v>12.24829618582113</v>
       </c>
       <c r="D27">
-        <v>12.8692784742921</v>
+        <v>12.92149618582113</v>
       </c>
       <c r="E27">
-        <v>1.485</v>
+        <v>1.6332</v>
       </c>
       <c r="F27">
-        <v>3.705</v>
+        <v>3.8532</v>
       </c>
       <c r="G27">
         <v>3.18</v>
@@ -3495,28 +3495,28 @@
         <v>2.061</v>
       </c>
       <c r="M27">
-        <v>0.191919</v>
+        <v>0.19959576</v>
       </c>
       <c r="N27">
-        <v>1.869081</v>
+        <v>1.86140424</v>
       </c>
       <c r="O27">
-        <v>0.5607243000000001</v>
+        <v>0.5584212720000001</v>
       </c>
       <c r="P27">
-        <v>1.3083567</v>
+        <v>1.302982968</v>
       </c>
       <c r="Q27">
-        <v>1.467356700000001</v>
+        <v>1.461982968</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.2213227155889029</v>
+        <v>0.2231176885752028</v>
       </c>
       <c r="T27">
-        <v>1.223822051514222</v>
+        <v>1.236337397548698</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>10.73890547574758</v>
+        <v>10.32587064975729</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1745346895456501</v>
+        <v>0.174012342399623</v>
       </c>
       <c r="C28">
-        <v>12.24829618582113</v>
+        <v>12.15273937546059</v>
       </c>
       <c r="D28">
-        <v>12.92149618582113</v>
+        <v>12.9741393754606</v>
       </c>
       <c r="E28">
-        <v>1.6332</v>
+        <v>1.7814</v>
       </c>
       <c r="F28">
-        <v>3.8532</v>
+        <v>4.0014</v>
       </c>
       <c r="G28">
         <v>3.18</v>
@@ -3577,28 +3577,28 @@
         <v>2.061</v>
       </c>
       <c r="M28">
-        <v>0.19959576</v>
+        <v>0.20727252</v>
       </c>
       <c r="N28">
-        <v>1.86140424</v>
+        <v>1.85372748</v>
       </c>
       <c r="O28">
-        <v>0.5584212720000001</v>
+        <v>0.5561182440000001</v>
       </c>
       <c r="P28">
-        <v>1.302982968</v>
+        <v>1.297609236</v>
       </c>
       <c r="Q28">
-        <v>1.461982968</v>
+        <v>1.456609236</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.2231176885752028</v>
+        <v>0.2249618389035932</v>
       </c>
       <c r="T28">
-        <v>1.236337397548698</v>
+        <v>1.249195629775901</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3615,7 +3615,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>10.32587064975729</v>
+        <v>9.943430996062576</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.174012342399623</v>
+        <v>0.173823195253596</v>
       </c>
       <c r="C29">
-        <v>12.15273937546059</v>
+        <v>12.02370794432942</v>
       </c>
       <c r="D29">
-        <v>12.9741393754606</v>
+        <v>12.99330794432942</v>
       </c>
       <c r="E29">
-        <v>1.7814</v>
+        <v>1.9296</v>
       </c>
       <c r="F29">
-        <v>4.0014</v>
+        <v>4.1496</v>
       </c>
       <c r="G29">
         <v>3.18</v>
@@ -3659,45 +3659,45 @@
         <v>2.061</v>
       </c>
       <c r="M29">
-        <v>0.20727252</v>
+        <v>0.2220036</v>
       </c>
       <c r="N29">
-        <v>1.85372748</v>
+        <v>1.8389964</v>
       </c>
       <c r="O29">
-        <v>0.5561182440000001</v>
+        <v>0.5516989200000001</v>
       </c>
       <c r="P29">
-        <v>1.297609236</v>
+        <v>1.28729748</v>
       </c>
       <c r="Q29">
-        <v>1.456609236</v>
+        <v>1.44629748</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.2249618389035932</v>
+        <v>0.2268572156299944</v>
       </c>
       <c r="T29">
-        <v>1.249195629775901</v>
+        <v>1.262411035120526</v>
       </c>
       <c r="U29">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V29">
         <v>0.3</v>
       </c>
       <c r="W29">
-        <v>0.03625999999999999</v>
+        <v>0.03745</v>
       </c>
       <c r="X29" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y29">
-        <v>9.943430996062576</v>
+        <v>9.283633238379918</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.173823195253596</v>
+        <v>0.1733127481075689</v>
       </c>
       <c r="C30">
-        <v>12.02370794432942</v>
+        <v>11.92752154340925</v>
       </c>
       <c r="D30">
-        <v>12.99330794432942</v>
+        <v>13.04532154340925</v>
       </c>
       <c r="E30">
-        <v>1.9296</v>
+        <v>2.0778</v>
       </c>
       <c r="F30">
-        <v>4.1496</v>
+        <v>4.297800000000001</v>
       </c>
       <c r="G30">
         <v>3.18</v>
@@ -3741,28 +3741,28 @@
         <v>2.061</v>
       </c>
       <c r="M30">
-        <v>0.2220036</v>
+        <v>0.2299323</v>
       </c>
       <c r="N30">
-        <v>1.8389964</v>
+        <v>1.8310677</v>
       </c>
       <c r="O30">
-        <v>0.5516989200000001</v>
+        <v>0.5493203100000001</v>
       </c>
       <c r="P30">
-        <v>1.28729748</v>
+        <v>1.28174739</v>
       </c>
       <c r="Q30">
-        <v>1.44629748</v>
+        <v>1.44074739</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.2268572156299944</v>
+        <v>0.228805983250097</v>
       </c>
       <c r="T30">
-        <v>1.262411035120526</v>
+        <v>1.275998705404436</v>
       </c>
       <c r="U30">
         <v>0.0535</v>
@@ -3779,7 +3779,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>9.283633238379918</v>
+        <v>8.963507954297853</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1733127481075689</v>
+        <v>0.1728023009615418</v>
       </c>
       <c r="C31">
-        <v>11.92752154340925</v>
+        <v>11.83175324819273</v>
       </c>
       <c r="D31">
-        <v>13.04532154340925</v>
+        <v>13.09775324819273</v>
       </c>
       <c r="E31">
-        <v>2.077799999999999</v>
+        <v>2.226</v>
       </c>
       <c r="F31">
-        <v>4.2978</v>
+        <v>4.446</v>
       </c>
       <c r="G31">
         <v>3.18</v>
@@ -3823,28 +3823,28 @@
         <v>2.061</v>
       </c>
       <c r="M31">
-        <v>0.2299323</v>
+        <v>0.237861</v>
       </c>
       <c r="N31">
-        <v>1.8310677</v>
+        <v>1.823139</v>
       </c>
       <c r="O31">
-        <v>0.5493203100000001</v>
+        <v>0.5469417000000001</v>
       </c>
       <c r="P31">
-        <v>1.28174739</v>
+        <v>1.2761973</v>
       </c>
       <c r="Q31">
-        <v>1.44074739</v>
+        <v>1.4351973</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.228805983250097</v>
+        <v>0.2308104299450598</v>
       </c>
       <c r="T31">
-        <v>1.275998705404436</v>
+        <v>1.289974594839315</v>
       </c>
       <c r="U31">
         <v>0.0535</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>8.963507954297855</v>
+        <v>8.664724355821258</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1728023009615418</v>
+        <v>0.1722918538155148</v>
       </c>
       <c r="C32">
-        <v>11.83175324819273</v>
+        <v>11.73640812037017</v>
       </c>
       <c r="D32">
-        <v>13.09775324819273</v>
+        <v>13.15060812037017</v>
       </c>
       <c r="E32">
-        <v>2.226</v>
+        <v>2.3742</v>
       </c>
       <c r="F32">
-        <v>4.446</v>
+        <v>4.5942</v>
       </c>
       <c r="G32">
         <v>3.18</v>
@@ -3905,28 +3905,28 @@
         <v>2.061</v>
       </c>
       <c r="M32">
-        <v>0.237861</v>
+        <v>0.2457897</v>
       </c>
       <c r="N32">
-        <v>1.823139</v>
+        <v>1.8152103</v>
       </c>
       <c r="O32">
-        <v>0.5469417000000001</v>
+        <v>0.5445630900000001</v>
       </c>
       <c r="P32">
-        <v>1.2761973</v>
+        <v>1.27064721</v>
       </c>
       <c r="Q32">
-        <v>1.4351973</v>
+        <v>1.42964721</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.2308104299450598</v>
+        <v>0.2328729765442243</v>
       </c>
       <c r="T32">
-        <v>1.289974594839315</v>
+        <v>1.304355582518683</v>
       </c>
       <c r="U32">
         <v>0.0535</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>8.664724355821258</v>
+        <v>8.385217118536701</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.1722918538155148</v>
+        <v>0.1717814066694877</v>
       </c>
       <c r="C33">
-        <v>11.73640812037017</v>
+        <v>11.64149130366701</v>
       </c>
       <c r="D33">
-        <v>13.15060812037017</v>
+        <v>13.203891303667</v>
       </c>
       <c r="E33">
-        <v>2.3742</v>
+        <v>2.5224</v>
       </c>
       <c r="F33">
-        <v>4.5942</v>
+        <v>4.7424</v>
       </c>
       <c r="G33">
         <v>3.18</v>
@@ -3987,28 +3987,28 @@
         <v>2.061</v>
       </c>
       <c r="M33">
-        <v>0.2457897</v>
+        <v>0.2537184</v>
       </c>
       <c r="N33">
-        <v>1.8152103</v>
+        <v>1.8072816</v>
       </c>
       <c r="O33">
-        <v>0.5445630900000001</v>
+        <v>0.5421844800000001</v>
       </c>
       <c r="P33">
-        <v>1.27064721</v>
+        <v>1.265097120000001</v>
       </c>
       <c r="Q33">
-        <v>1.42964721</v>
+        <v>1.424097120000001</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.2328729765442243</v>
+        <v>0.2349961862786584</v>
       </c>
       <c r="T33">
-        <v>1.304355582518683</v>
+        <v>1.319159540423914</v>
       </c>
       <c r="U33">
         <v>0.0535</v>
@@ -4025,7 +4025,7 @@
         </is>
       </c>
       <c r="Y33">
-        <v>8.385217118536701</v>
+        <v>8.12317908358243</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1717814066694877</v>
+        <v>0.1712709595234606</v>
       </c>
       <c r="C34">
-        <v>11.64149130366701</v>
+        <v>11.54700802551249</v>
       </c>
       <c r="D34">
-        <v>13.203891303667</v>
+        <v>13.25760802551249</v>
       </c>
       <c r="E34">
-        <v>2.5224</v>
+        <v>2.6706</v>
       </c>
       <c r="F34">
-        <v>4.7424</v>
+        <v>4.8906</v>
       </c>
       <c r="G34">
         <v>3.18</v>
@@ -4069,28 +4069,28 @@
         <v>2.061</v>
       </c>
       <c r="M34">
-        <v>0.2537184</v>
+        <v>0.2616471</v>
       </c>
       <c r="N34">
-        <v>1.8072816</v>
+        <v>1.7993529</v>
       </c>
       <c r="O34">
-        <v>0.5421844800000001</v>
+        <v>0.5398058700000001</v>
       </c>
       <c r="P34">
-        <v>1.265097120000001</v>
+        <v>1.25954703</v>
       </c>
       <c r="Q34">
-        <v>1.424097120000001</v>
+        <v>1.41854703</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.2349961862786584</v>
+        <v>0.2371827754081502</v>
       </c>
       <c r="T34">
-        <v>1.319159540423914</v>
+        <v>1.334405407520347</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>8.12317908358243</v>
+        <v>7.877022141655689</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1712709595234606</v>
+        <v>0.1707605123774336</v>
       </c>
       <c r="C35">
-        <v>11.54700802551249</v>
+        <v>11.45296359874933</v>
       </c>
       <c r="D35">
-        <v>13.25760802551249</v>
+        <v>13.31176359874932</v>
       </c>
       <c r="E35">
-        <v>2.6706</v>
+        <v>2.8188</v>
       </c>
       <c r="F35">
-        <v>4.8906</v>
+        <v>5.0388</v>
       </c>
       <c r="G35">
         <v>3.18</v>
@@ -4151,28 +4151,28 @@
         <v>2.061</v>
       </c>
       <c r="M35">
-        <v>0.2616471</v>
+        <v>0.2695758</v>
       </c>
       <c r="N35">
-        <v>1.7993529</v>
+        <v>1.7914242</v>
       </c>
       <c r="O35">
-        <v>0.5398058700000001</v>
+        <v>0.5374272600000001</v>
       </c>
       <c r="P35">
-        <v>1.25954703</v>
+        <v>1.25399694</v>
       </c>
       <c r="Q35">
-        <v>1.41854703</v>
+        <v>1.41299694</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.2371827754081502</v>
+        <v>0.2394356248142933</v>
       </c>
       <c r="T35">
-        <v>1.334405407520347</v>
+        <v>1.350113270589399</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>7.877022141655689</v>
+        <v>7.645345019842288</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1707605123774336</v>
+        <v>0.1704460652314065</v>
       </c>
       <c r="C36">
-        <v>11.45296359874933</v>
+        <v>11.33834545361528</v>
       </c>
       <c r="D36">
-        <v>13.31176359874932</v>
+        <v>13.34534545361528</v>
       </c>
       <c r="E36">
-        <v>2.8188</v>
+        <v>2.967</v>
       </c>
       <c r="F36">
-        <v>5.0388</v>
+        <v>5.187</v>
       </c>
       <c r="G36">
         <v>3.18</v>
@@ -4233,45 +4233,45 @@
         <v>2.061</v>
       </c>
       <c r="M36">
-        <v>0.2695758</v>
+        <v>0.2816541</v>
       </c>
       <c r="N36">
-        <v>1.7914242</v>
+        <v>1.7793459</v>
       </c>
       <c r="O36">
-        <v>0.5374272600000001</v>
+        <v>0.5338037700000001</v>
       </c>
       <c r="P36">
-        <v>1.25399694</v>
+        <v>1.24554213</v>
       </c>
       <c r="Q36">
-        <v>1.41299694</v>
+        <v>1.40454213</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.2394356248142933</v>
+        <v>0.2417577926637024</v>
       </c>
       <c r="T36">
-        <v>1.350113270589399</v>
+        <v>1.366304452522114</v>
       </c>
       <c r="U36">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V36">
         <v>0.3</v>
       </c>
       <c r="W36">
-        <v>0.03745</v>
+        <v>0.03801</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y36">
-        <v>7.645345019842288</v>
+        <v>7.317486235776438</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1704460652314065</v>
+        <v>0.1699412180853794</v>
       </c>
       <c r="C37">
-        <v>11.33834545361528</v>
+        <v>11.24441719082645</v>
       </c>
       <c r="D37">
-        <v>13.34534545361528</v>
+        <v>13.39961719082645</v>
       </c>
       <c r="E37">
-        <v>2.967</v>
+        <v>3.1152</v>
       </c>
       <c r="F37">
-        <v>5.187</v>
+        <v>5.3352</v>
       </c>
       <c r="G37">
         <v>3.18</v>
@@ -4315,28 +4315,28 @@
         <v>2.061</v>
       </c>
       <c r="M37">
-        <v>0.2816541</v>
+        <v>0.28970136</v>
       </c>
       <c r="N37">
-        <v>1.7793459</v>
+        <v>1.77129864</v>
       </c>
       <c r="O37">
-        <v>0.5338037700000001</v>
+        <v>0.5313895920000001</v>
       </c>
       <c r="P37">
-        <v>1.24554213</v>
+        <v>1.239909048</v>
       </c>
       <c r="Q37">
-        <v>1.40454213</v>
+        <v>1.398909048</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.2417577926637024</v>
+        <v>0.2441525282584054</v>
       </c>
       <c r="T37">
-        <v>1.366304452522114</v>
+        <v>1.383001608890227</v>
       </c>
       <c r="U37">
         <v>0.0543</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>7.317486235776438</v>
+        <v>7.114222729227092</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.1699412180853795</v>
+        <v>0.1694363709393524</v>
       </c>
       <c r="C38">
-        <v>11.24441719082644</v>
+        <v>11.15093214602326</v>
       </c>
       <c r="D38">
-        <v>13.39961719082644</v>
+        <v>13.45433214602326</v>
       </c>
       <c r="E38">
-        <v>3.115199999999999</v>
+        <v>3.263399999999999</v>
       </c>
       <c r="F38">
-        <v>5.335199999999999</v>
+        <v>5.4834</v>
       </c>
       <c r="G38">
         <v>3.18</v>
@@ -4397,28 +4397,28 @@
         <v>2.061</v>
       </c>
       <c r="M38">
-        <v>0.28970136</v>
+        <v>0.29774862</v>
       </c>
       <c r="N38">
-        <v>1.77129864</v>
+        <v>1.76325138</v>
       </c>
       <c r="O38">
-        <v>0.5313895920000001</v>
+        <v>0.5289754140000001</v>
       </c>
       <c r="P38">
-        <v>1.239909048</v>
+        <v>1.234275966</v>
       </c>
       <c r="Q38">
-        <v>1.398909048</v>
+        <v>1.393275966</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.2441525282584054</v>
+        <v>0.2466232872053213</v>
       </c>
       <c r="T38">
-        <v>1.383001608890227</v>
+        <v>1.400228833714469</v>
       </c>
       <c r="U38">
         <v>0.0543</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>7.114222729227093</v>
+        <v>6.921946439247983</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1694363709393524</v>
+        <v>0.1689315237933253</v>
       </c>
       <c r="C39">
-        <v>11.15093214602326</v>
+        <v>11.05789577087225</v>
       </c>
       <c r="D39">
-        <v>13.45433214602326</v>
+        <v>13.50949577087225</v>
       </c>
       <c r="E39">
-        <v>3.263399999999999</v>
+        <v>3.4116</v>
       </c>
       <c r="F39">
-        <v>5.4834</v>
+        <v>5.631600000000001</v>
       </c>
       <c r="G39">
         <v>3.18</v>
@@ -4479,28 +4479,28 @@
         <v>2.061</v>
       </c>
       <c r="M39">
-        <v>0.29774862</v>
+        <v>0.30579588</v>
       </c>
       <c r="N39">
-        <v>1.76325138</v>
+        <v>1.75520412</v>
       </c>
       <c r="O39">
-        <v>0.5289754140000001</v>
+        <v>0.526561236</v>
       </c>
       <c r="P39">
-        <v>1.234275966</v>
+        <v>1.228642884</v>
       </c>
       <c r="Q39">
-        <v>1.393275966</v>
+        <v>1.387642884</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.2466232872053213</v>
+        <v>0.2491737480537506</v>
       </c>
       <c r="T39">
-        <v>1.400228833714469</v>
+        <v>1.418011775468527</v>
       </c>
       <c r="U39">
         <v>0.0543</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>6.921946439247983</v>
+        <v>6.739789954004613</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1689315237933253</v>
+        <v>0.1684266766472983</v>
       </c>
       <c r="C40">
-        <v>11.05789577087225</v>
+        <v>10.96531360681676</v>
       </c>
       <c r="D40">
-        <v>13.50949577087225</v>
+        <v>13.56511360681676</v>
       </c>
       <c r="E40">
-        <v>3.4116</v>
+        <v>3.559800000000001</v>
       </c>
       <c r="F40">
-        <v>5.631600000000001</v>
+        <v>5.779800000000001</v>
       </c>
       <c r="G40">
         <v>3.18</v>
@@ -4561,28 +4561,28 @@
         <v>2.061</v>
       </c>
       <c r="M40">
-        <v>0.30579588</v>
+        <v>0.31384314</v>
       </c>
       <c r="N40">
-        <v>1.75520412</v>
+        <v>1.74715686</v>
       </c>
       <c r="O40">
-        <v>0.526561236</v>
+        <v>0.5241470580000002</v>
       </c>
       <c r="P40">
-        <v>1.228642884</v>
+        <v>1.223009802</v>
       </c>
       <c r="Q40">
-        <v>1.387642884</v>
+        <v>1.382009802</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.2491737480537506</v>
+        <v>0.2518078305693415</v>
       </c>
       <c r="T40">
-        <v>1.418011775468527</v>
+        <v>1.436377764493209</v>
       </c>
       <c r="U40">
         <v>0.0543</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>6.739789954004613</v>
+        <v>6.566974826978854</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1684266766472983</v>
+        <v>0.1679218295012712</v>
       </c>
       <c r="C41">
-        <v>10.96531360681676</v>
+        <v>10.87319128693261</v>
       </c>
       <c r="D41">
-        <v>13.56511360681676</v>
+        <v>13.62119128693261</v>
       </c>
       <c r="E41">
-        <v>3.559800000000001</v>
+        <v>3.708000000000001</v>
       </c>
       <c r="F41">
-        <v>5.779800000000001</v>
+        <v>5.928000000000001</v>
       </c>
       <c r="G41">
         <v>3.18</v>
@@ -4643,28 +4643,28 @@
         <v>2.061</v>
       </c>
       <c r="M41">
-        <v>0.31384314</v>
+        <v>0.3218904000000001</v>
       </c>
       <c r="N41">
-        <v>1.74715686</v>
+        <v>1.7391096</v>
       </c>
       <c r="O41">
-        <v>0.5241470580000002</v>
+        <v>0.5217328800000001</v>
       </c>
       <c r="P41">
-        <v>1.223009802</v>
+        <v>1.21737672</v>
       </c>
       <c r="Q41">
-        <v>1.382009802</v>
+        <v>1.37637672</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2518078305693415</v>
+        <v>0.254529715835452</v>
       </c>
       <c r="T41">
-        <v>1.436377764493209</v>
+        <v>1.455355953152047</v>
       </c>
       <c r="U41">
         <v>0.0543</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>6.566974826978854</v>
+        <v>6.402800456304382</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1679218295012712</v>
+        <v>0.1674169823552442</v>
       </c>
       <c r="C42">
-        <v>10.87319128693261</v>
+        <v>10.78153453783</v>
       </c>
       <c r="D42">
-        <v>13.62119128693261</v>
+        <v>13.67773453783</v>
       </c>
       <c r="E42">
-        <v>3.708000000000001</v>
+        <v>3.856200000000001</v>
       </c>
       <c r="F42">
-        <v>5.928000000000001</v>
+        <v>6.076200000000001</v>
       </c>
       <c r="G42">
         <v>3.18</v>
@@ -4725,28 +4725,28 @@
         <v>2.061</v>
       </c>
       <c r="M42">
-        <v>0.3218904000000001</v>
+        <v>0.3299376600000001</v>
       </c>
       <c r="N42">
-        <v>1.7391096</v>
+        <v>1.73106234</v>
       </c>
       <c r="O42">
-        <v>0.5217328800000001</v>
+        <v>0.5193187020000001</v>
       </c>
       <c r="P42">
-        <v>1.21737672</v>
+        <v>1.211743638</v>
       </c>
       <c r="Q42">
-        <v>1.37637672</v>
+        <v>1.370743638</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.254529715835452</v>
+        <v>0.2573438683987189</v>
       </c>
       <c r="T42">
-        <v>1.455355953152047</v>
+        <v>1.474977470239998</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4763,7 +4763,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>6.402800456304382</v>
+        <v>6.24663459151647</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.1674169823552442</v>
+        <v>0.1672061352092171</v>
       </c>
       <c r="C43">
-        <v>10.78153453783</v>
+        <v>10.65708878456924</v>
       </c>
       <c r="D43">
-        <v>13.67773453783</v>
+        <v>13.70148878456924</v>
       </c>
       <c r="E43">
-        <v>3.856200000000001</v>
+        <v>4.0044</v>
       </c>
       <c r="F43">
-        <v>6.076200000000001</v>
+        <v>6.224400000000001</v>
       </c>
       <c r="G43">
         <v>3.18</v>
@@ -4807,45 +4807,45 @@
         <v>2.061</v>
       </c>
       <c r="M43">
-        <v>0.3299376600000001</v>
+        <v>0.3442093200000001</v>
       </c>
       <c r="N43">
-        <v>1.73106234</v>
+        <v>1.71679068</v>
       </c>
       <c r="O43">
-        <v>0.5193187020000001</v>
+        <v>0.5150372040000001</v>
       </c>
       <c r="P43">
-        <v>1.211743638</v>
+        <v>1.201753476</v>
       </c>
       <c r="Q43">
-        <v>1.370743638</v>
+        <v>1.360753476</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2573438683987189</v>
+        <v>0.2602550607055467</v>
       </c>
       <c r="T43">
-        <v>1.474977470239998</v>
+        <v>1.495275591365465</v>
       </c>
       <c r="U43">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V43">
         <v>0.3</v>
       </c>
       <c r="W43">
-        <v>0.03801</v>
+        <v>0.03871</v>
       </c>
       <c r="X43" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y43">
-        <v>6.24663459151647</v>
+        <v>5.987635663090122</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1672061352092171</v>
+        <v>0.1667082880631901</v>
       </c>
       <c r="C44">
-        <v>10.65708878456924</v>
+        <v>10.56530548847753</v>
       </c>
       <c r="D44">
-        <v>13.70148878456924</v>
+        <v>13.75790548847753</v>
       </c>
       <c r="E44">
-        <v>4.0044</v>
+        <v>4.1526</v>
       </c>
       <c r="F44">
-        <v>6.2244</v>
+        <v>6.3726</v>
       </c>
       <c r="G44">
         <v>3.18</v>
@@ -4889,28 +4889,28 @@
         <v>2.061</v>
       </c>
       <c r="M44">
-        <v>0.34420932</v>
+        <v>0.35240478</v>
       </c>
       <c r="N44">
-        <v>1.71679068</v>
+        <v>1.70859522</v>
       </c>
       <c r="O44">
-        <v>0.5150372040000001</v>
+        <v>0.5125785660000001</v>
       </c>
       <c r="P44">
-        <v>1.201753476</v>
+        <v>1.196016654</v>
       </c>
       <c r="Q44">
-        <v>1.360753476</v>
+        <v>1.355016654</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2602550607055467</v>
+        <v>0.2632684001108597</v>
       </c>
       <c r="T44">
-        <v>1.495275591365465</v>
+        <v>1.516285927267264</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>5.987635663090122</v>
+        <v>5.848388322088026</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1667082880631901</v>
+        <v>0.166210440917163</v>
       </c>
       <c r="C45">
-        <v>10.56530548847753</v>
+        <v>10.47398871164803</v>
       </c>
       <c r="D45">
-        <v>13.75790548847753</v>
+        <v>13.81478871164803</v>
       </c>
       <c r="E45">
-        <v>4.1526</v>
+        <v>4.300800000000001</v>
       </c>
       <c r="F45">
-        <v>6.3726</v>
+        <v>6.5208</v>
       </c>
       <c r="G45">
         <v>3.18</v>
@@ -4971,28 +4971,28 @@
         <v>2.061</v>
       </c>
       <c r="M45">
-        <v>0.35240478</v>
+        <v>0.36060024</v>
       </c>
       <c r="N45">
-        <v>1.70859522</v>
+        <v>1.70039976</v>
       </c>
       <c r="O45">
-        <v>0.5125785660000001</v>
+        <v>0.5101199280000001</v>
       </c>
       <c r="P45">
-        <v>1.196016654</v>
+        <v>1.190279832</v>
       </c>
       <c r="Q45">
-        <v>1.355016654</v>
+        <v>1.349279832</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2632684001108597</v>
+        <v>0.2663893587806481</v>
       </c>
       <c r="T45">
-        <v>1.516285927267264</v>
+        <v>1.538046632308413</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>5.848388322088026</v>
+        <v>5.715470405676935</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.166210440917163</v>
+        <v>0.1657125937711359</v>
       </c>
       <c r="C46">
-        <v>10.47398871164803</v>
+        <v>10.38314426469517</v>
       </c>
       <c r="D46">
-        <v>13.81478871164803</v>
+        <v>13.87214426469517</v>
       </c>
       <c r="E46">
-        <v>4.300800000000001</v>
+        <v>4.449</v>
       </c>
       <c r="F46">
-        <v>6.5208</v>
+        <v>6.669</v>
       </c>
       <c r="G46">
         <v>3.18</v>
@@ -5053,28 +5053,28 @@
         <v>2.061</v>
       </c>
       <c r="M46">
-        <v>0.36060024</v>
+        <v>0.3687957000000001</v>
       </c>
       <c r="N46">
-        <v>1.70039976</v>
+        <v>1.6922043</v>
       </c>
       <c r="O46">
-        <v>0.5101199280000001</v>
+        <v>0.50766129</v>
       </c>
       <c r="P46">
-        <v>1.190279832</v>
+        <v>1.18454301</v>
       </c>
       <c r="Q46">
-        <v>1.349279832</v>
+        <v>1.34354301</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2663893587806481</v>
+        <v>0.2696238068566107</v>
       </c>
       <c r="T46">
-        <v>1.538046632308413</v>
+        <v>1.560598635714695</v>
       </c>
       <c r="U46">
         <v>0.0553</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>5.715470405676935</v>
+        <v>5.588459952217447</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1657125937711359</v>
+        <v>0.1652147466251089</v>
       </c>
       <c r="C47">
-        <v>10.38314426469517</v>
+        <v>10.29277805513259</v>
       </c>
       <c r="D47">
-        <v>13.87214426469517</v>
+        <v>13.92997805513259</v>
       </c>
       <c r="E47">
-        <v>4.449</v>
+        <v>4.597200000000001</v>
       </c>
       <c r="F47">
-        <v>6.669</v>
+        <v>6.817200000000001</v>
       </c>
       <c r="G47">
         <v>3.18</v>
@@ -5135,28 +5135,28 @@
         <v>2.061</v>
       </c>
       <c r="M47">
-        <v>0.3687957000000001</v>
+        <v>0.37699116</v>
       </c>
       <c r="N47">
-        <v>1.6922043</v>
+        <v>1.68400884</v>
       </c>
       <c r="O47">
-        <v>0.50766129</v>
+        <v>0.5052026520000001</v>
       </c>
       <c r="P47">
-        <v>1.18454301</v>
+        <v>1.178806188</v>
       </c>
       <c r="Q47">
-        <v>1.34354301</v>
+        <v>1.337806188</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2696238068566107</v>
+        <v>0.2729780493057571</v>
       </c>
       <c r="T47">
-        <v>1.560598635714695</v>
+        <v>1.583985898506395</v>
       </c>
       <c r="U47">
         <v>0.0553</v>
@@ -5173,7 +5173,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>5.588459952217447</v>
+        <v>5.466971692386633</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1652147466251089</v>
+        <v>0.1647168994790818</v>
       </c>
       <c r="C48">
-        <v>10.29277805513259</v>
+        <v>10.20289608940145</v>
       </c>
       <c r="D48">
-        <v>13.92997805513259</v>
+        <v>13.98829608940145</v>
       </c>
       <c r="E48">
-        <v>4.597200000000001</v>
+        <v>4.7454</v>
       </c>
       <c r="F48">
-        <v>6.817200000000001</v>
+        <v>6.965400000000001</v>
       </c>
       <c r="G48">
         <v>3.18</v>
@@ -5217,28 +5217,28 @@
         <v>2.061</v>
       </c>
       <c r="M48">
-        <v>0.37699116</v>
+        <v>0.38518662</v>
       </c>
       <c r="N48">
-        <v>1.68400884</v>
+        <v>1.67581338</v>
       </c>
       <c r="O48">
-        <v>0.5052026520000001</v>
+        <v>0.5027440140000001</v>
       </c>
       <c r="P48">
-        <v>1.178806188</v>
+        <v>1.173069366</v>
       </c>
       <c r="Q48">
-        <v>1.337806188</v>
+        <v>1.332069366</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2729780493057571</v>
+        <v>0.2764588669416638</v>
       </c>
       <c r="T48">
-        <v>1.583985898506395</v>
+        <v>1.608255699516649</v>
       </c>
       <c r="U48">
         <v>0.0553</v>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>5.466971692386633</v>
+        <v>5.350653145740109</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1647168994790818</v>
+        <v>0.1642190523330548</v>
       </c>
       <c r="C49">
-        <v>10.20289608940145</v>
+        <v>10.11350447494994</v>
       </c>
       <c r="D49">
-        <v>13.98829608940145</v>
+        <v>14.04710447494994</v>
       </c>
       <c r="E49">
-        <v>4.7454</v>
+        <v>4.893600000000001</v>
       </c>
       <c r="F49">
-        <v>6.965400000000001</v>
+        <v>7.113600000000001</v>
       </c>
       <c r="G49">
         <v>3.18</v>
@@ -5299,28 +5299,28 @@
         <v>2.061</v>
       </c>
       <c r="M49">
-        <v>0.38518662</v>
+        <v>0.3933820800000001</v>
       </c>
       <c r="N49">
-        <v>1.67581338</v>
+        <v>1.66761792</v>
       </c>
       <c r="O49">
-        <v>0.5027440140000001</v>
+        <v>0.5002853760000001</v>
       </c>
       <c r="P49">
-        <v>1.173069366</v>
+        <v>1.167332544</v>
       </c>
       <c r="Q49">
-        <v>1.332069366</v>
+        <v>1.326332544</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.2764588669416638</v>
+        <v>0.2800735621789514</v>
       </c>
       <c r="T49">
-        <v>1.608255699516649</v>
+        <v>1.633458954411913</v>
       </c>
       <c r="U49">
         <v>0.0553</v>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>5.350653145740109</v>
+        <v>5.239181205203857</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1642190523330548</v>
+        <v>0.1637212051870277</v>
       </c>
       <c r="C50">
-        <v>10.11350447494994</v>
+        <v>10.02460942236552</v>
       </c>
       <c r="D50">
-        <v>14.04710447494994</v>
+        <v>14.10640942236552</v>
       </c>
       <c r="E50">
-        <v>4.893599999999999</v>
+        <v>5.0418</v>
       </c>
       <c r="F50">
-        <v>7.1136</v>
+        <v>7.2618</v>
       </c>
       <c r="G50">
         <v>3.18</v>
@@ -5381,28 +5381,28 @@
         <v>2.061</v>
       </c>
       <c r="M50">
-        <v>0.39338208</v>
+        <v>0.40157754</v>
       </c>
       <c r="N50">
-        <v>1.66761792</v>
+        <v>1.65942246</v>
       </c>
       <c r="O50">
-        <v>0.5002853760000001</v>
+        <v>0.4978267380000001</v>
       </c>
       <c r="P50">
-        <v>1.167332544</v>
+        <v>1.161595722</v>
       </c>
       <c r="Q50">
-        <v>1.326332544</v>
+        <v>1.320595722</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2800735621789514</v>
+        <v>0.2838300101706425</v>
       </c>
       <c r="T50">
-        <v>1.633458954411913</v>
+        <v>1.659650572244246</v>
       </c>
       <c r="U50">
         <v>0.0553</v>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>5.239181205203857</v>
+        <v>5.132259139791534</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1637212051870277</v>
+        <v>0.1632233580410006</v>
       </c>
       <c r="C51">
-        <v>10.02460942236552</v>
+        <v>9.93621724756127</v>
       </c>
       <c r="D51">
-        <v>14.10640942236552</v>
+        <v>14.16621724756127</v>
       </c>
       <c r="E51">
-        <v>5.0418</v>
+        <v>5.19</v>
       </c>
       <c r="F51">
-        <v>7.2618</v>
+        <v>7.41</v>
       </c>
       <c r="G51">
         <v>3.18</v>
@@ -5463,28 +5463,28 @@
         <v>2.061</v>
       </c>
       <c r="M51">
-        <v>0.40157754</v>
+        <v>0.409773</v>
       </c>
       <c r="N51">
-        <v>1.65942246</v>
+        <v>1.651227</v>
       </c>
       <c r="O51">
-        <v>0.4978267380000001</v>
+        <v>0.4953681000000001</v>
       </c>
       <c r="P51">
-        <v>1.161595722</v>
+        <v>1.1558589</v>
       </c>
       <c r="Q51">
-        <v>1.320595722</v>
+        <v>1.3148589</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.2838300101706425</v>
+        <v>0.2877367160820012</v>
       </c>
       <c r="T51">
-        <v>1.659650572244246</v>
+        <v>1.686889854789873</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.132259139791534</v>
+        <v>5.029613956995703</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1632233580410006</v>
+        <v>0.1627255108949736</v>
       </c>
       <c r="C52">
-        <v>9.93621724756127</v>
+        <v>9.848334374018236</v>
       </c>
       <c r="D52">
-        <v>14.16621724756127</v>
+        <v>14.22653437401824</v>
       </c>
       <c r="E52">
-        <v>5.19</v>
+        <v>5.338200000000001</v>
       </c>
       <c r="F52">
-        <v>7.41</v>
+        <v>7.5582</v>
       </c>
       <c r="G52">
         <v>3.18</v>
@@ -5545,28 +5545,28 @@
         <v>2.061</v>
       </c>
       <c r="M52">
-        <v>0.409773</v>
+        <v>0.41796846</v>
       </c>
       <c r="N52">
-        <v>1.651227</v>
+        <v>1.64303154</v>
       </c>
       <c r="O52">
-        <v>0.4953681000000001</v>
+        <v>0.4929094620000001</v>
       </c>
       <c r="P52">
-        <v>1.1558589</v>
+        <v>1.150122078</v>
       </c>
       <c r="Q52">
-        <v>1.3148589</v>
+        <v>1.309122078</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2877367160820012</v>
+        <v>0.291802879377497</v>
       </c>
       <c r="T52">
-        <v>1.686889854789873</v>
+        <v>1.715240944786341</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.029613956995703</v>
+        <v>4.930994075485984</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1627255108949736</v>
+        <v>0.1622276637489465</v>
       </c>
       <c r="C53">
-        <v>9.848334374018236</v>
+        <v>9.760967335085232</v>
       </c>
       <c r="D53">
-        <v>14.22653437401824</v>
+        <v>14.28736733508523</v>
       </c>
       <c r="E53">
-        <v>5.338200000000001</v>
+        <v>5.4864</v>
       </c>
       <c r="F53">
-        <v>7.5582</v>
+        <v>7.7064</v>
       </c>
       <c r="G53">
         <v>3.18</v>
@@ -5627,28 +5627,28 @@
         <v>2.061</v>
       </c>
       <c r="M53">
-        <v>0.41796846</v>
+        <v>0.42616392</v>
       </c>
       <c r="N53">
-        <v>1.64303154</v>
+        <v>1.63483608</v>
       </c>
       <c r="O53">
-        <v>0.4929094620000001</v>
+        <v>0.4904508240000001</v>
       </c>
       <c r="P53">
-        <v>1.150122078</v>
+        <v>1.144385256</v>
       </c>
       <c r="Q53">
-        <v>1.309122078</v>
+        <v>1.303385256</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.291802879377497</v>
+        <v>0.2960384661436385</v>
       </c>
       <c r="T53">
-        <v>1.715240944786341</v>
+        <v>1.744773330199329</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>4.930994075485984</v>
+        <v>4.836167266342022</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1622276637489465</v>
+        <v>0.1617298166029195</v>
       </c>
       <c r="C54">
-        <v>9.760967335085232</v>
+        <v>9.674122776337889</v>
       </c>
       <c r="D54">
-        <v>14.28736733508523</v>
+        <v>14.34872277633789</v>
       </c>
       <c r="E54">
-        <v>5.4864</v>
+        <v>5.634600000000001</v>
       </c>
       <c r="F54">
-        <v>7.7064</v>
+        <v>7.8546</v>
       </c>
       <c r="G54">
         <v>3.18</v>
@@ -5709,28 +5709,28 @@
         <v>2.061</v>
       </c>
       <c r="M54">
-        <v>0.42616392</v>
+        <v>0.43435938</v>
       </c>
       <c r="N54">
-        <v>1.63483608</v>
+        <v>1.62664062</v>
       </c>
       <c r="O54">
-        <v>0.4904508240000001</v>
+        <v>0.487992186</v>
       </c>
       <c r="P54">
-        <v>1.144385256</v>
+        <v>1.138648434</v>
       </c>
       <c r="Q54">
-        <v>1.303385256</v>
+        <v>1.297648434</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2960384661436385</v>
+        <v>0.3004542906445095</v>
       </c>
       <c r="T54">
-        <v>1.744773330199329</v>
+        <v>1.775562412863934</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5747,7 +5747,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>4.836167266342022</v>
+        <v>4.744918827354437</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.1617298166029195</v>
+        <v>0.1612319694568924</v>
       </c>
       <c r="C55">
-        <v>9.674122776337889</v>
+        <v>9.587807457998814</v>
       </c>
       <c r="D55">
-        <v>14.34872277633789</v>
+        <v>14.41060745799881</v>
       </c>
       <c r="E55">
-        <v>5.634600000000001</v>
+        <v>5.7828</v>
       </c>
       <c r="F55">
-        <v>7.8546</v>
+        <v>8.002800000000001</v>
       </c>
       <c r="G55">
         <v>3.18</v>
@@ -5791,28 +5791,28 @@
         <v>2.061</v>
       </c>
       <c r="M55">
-        <v>0.43435938</v>
+        <v>0.4425548400000001</v>
       </c>
       <c r="N55">
-        <v>1.62664062</v>
+        <v>1.61844516</v>
       </c>
       <c r="O55">
-        <v>0.487992186</v>
+        <v>0.485533548</v>
       </c>
       <c r="P55">
-        <v>1.138648434</v>
+        <v>1.132911612</v>
       </c>
       <c r="Q55">
-        <v>1.297648434</v>
+        <v>1.291911612</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.3004542906445095</v>
+        <v>0.3050621075149834</v>
       </c>
       <c r="T55">
-        <v>1.775562412863934</v>
+        <v>1.807690151296564</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>4.744918827354437</v>
+        <v>4.657049960181206</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.1612319694568924</v>
+        <v>0.1607341223108653</v>
       </c>
       <c r="C56">
-        <v>9.587807457998814</v>
+        <v>9.502028257420561</v>
       </c>
       <c r="D56">
-        <v>14.41060745799881</v>
+        <v>14.47302825742056</v>
       </c>
       <c r="E56">
-        <v>5.7828</v>
+        <v>5.931000000000001</v>
       </c>
       <c r="F56">
-        <v>8.002800000000001</v>
+        <v>8.151000000000002</v>
       </c>
       <c r="G56">
         <v>3.18</v>
@@ -5873,28 +5873,28 @@
         <v>2.061</v>
       </c>
       <c r="M56">
-        <v>0.4425548400000001</v>
+        <v>0.4507503000000001</v>
       </c>
       <c r="N56">
-        <v>1.61844516</v>
+        <v>1.6102497</v>
       </c>
       <c r="O56">
-        <v>0.485533548</v>
+        <v>0.48307491</v>
       </c>
       <c r="P56">
-        <v>1.132911612</v>
+        <v>1.12717479</v>
       </c>
       <c r="Q56">
-        <v>1.291911612</v>
+        <v>1.28617479</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.3050621075149834</v>
+        <v>0.3098747162463674</v>
       </c>
       <c r="T56">
-        <v>1.807690151296564</v>
+        <v>1.84124578921509</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>4.657049960181206</v>
+        <v>4.572376324541548</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.1607341223108653</v>
+        <v>0.1612162751648382</v>
       </c>
       <c r="C57">
-        <v>9.502028257420561</v>
+        <v>9.293367010772462</v>
       </c>
       <c r="D57">
-        <v>14.47302825742056</v>
+        <v>14.41256701077246</v>
       </c>
       <c r="E57">
-        <v>5.931000000000001</v>
+        <v>6.0792</v>
       </c>
       <c r="F57">
-        <v>8.151000000000002</v>
+        <v>8.299200000000001</v>
       </c>
       <c r="G57">
         <v>3.18</v>
@@ -5955,45 +5955,45 @@
         <v>2.061</v>
       </c>
       <c r="M57">
-        <v>0.4507503000000001</v>
+        <v>0.4796937600000001</v>
       </c>
       <c r="N57">
-        <v>1.6102497</v>
+        <v>1.58130624</v>
       </c>
       <c r="O57">
-        <v>0.48307491</v>
+        <v>0.4743918720000001</v>
       </c>
       <c r="P57">
-        <v>1.12717479</v>
+        <v>1.106914368</v>
       </c>
       <c r="Q57">
-        <v>1.28617479</v>
+        <v>1.265914368</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.3098747162463674</v>
+        <v>0.314906079920087</v>
       </c>
       <c r="T57">
-        <v>1.84124578921509</v>
+        <v>1.87632668340264</v>
       </c>
       <c r="U57">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V57">
         <v>0.3</v>
       </c>
       <c r="W57">
-        <v>0.03871</v>
+        <v>0.04046</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y57">
-        <v>4.572376324541548</v>
+        <v>4.296491161360949</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.1612162751648382</v>
+        <v>0.1607359280188112</v>
       </c>
       <c r="C58">
-        <v>9.293367010772462</v>
+        <v>9.20540087802253</v>
       </c>
       <c r="D58">
-        <v>14.41256701077246</v>
+        <v>14.47280087802253</v>
       </c>
       <c r="E58">
-        <v>6.0792</v>
+        <v>6.227400000000001</v>
       </c>
       <c r="F58">
-        <v>8.299200000000001</v>
+        <v>8.447400000000002</v>
       </c>
       <c r="G58">
         <v>3.18</v>
@@ -6037,28 +6037,28 @@
         <v>2.061</v>
       </c>
       <c r="M58">
-        <v>0.4796937600000001</v>
+        <v>0.4882597200000001</v>
       </c>
       <c r="N58">
-        <v>1.58130624</v>
+        <v>1.57274028</v>
       </c>
       <c r="O58">
-        <v>0.4743918720000001</v>
+        <v>0.4718220840000001</v>
       </c>
       <c r="P58">
-        <v>1.106914368</v>
+        <v>1.100918196</v>
       </c>
       <c r="Q58">
-        <v>1.265914368</v>
+        <v>1.259918196</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.314906079920087</v>
+        <v>0.3201714605088632</v>
       </c>
       <c r="T58">
-        <v>1.87632668340264</v>
+        <v>1.913039247087284</v>
       </c>
       <c r="U58">
         <v>0.0578</v>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>4.296491161360949</v>
+        <v>4.221114123442335</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.1607359280188112</v>
+        <v>0.1602555808727841</v>
       </c>
       <c r="C59">
-        <v>9.20540087802253</v>
+        <v>9.117940324223088</v>
       </c>
       <c r="D59">
-        <v>14.47280087802253</v>
+        <v>14.53354032422309</v>
       </c>
       <c r="E59">
-        <v>6.227400000000001</v>
+        <v>6.3756</v>
       </c>
       <c r="F59">
-        <v>8.447400000000002</v>
+        <v>8.595600000000001</v>
       </c>
       <c r="G59">
         <v>3.18</v>
@@ -6119,28 +6119,28 @@
         <v>2.061</v>
       </c>
       <c r="M59">
-        <v>0.4882597200000001</v>
+        <v>0.4968256800000001</v>
       </c>
       <c r="N59">
-        <v>1.57274028</v>
+        <v>1.56417432</v>
       </c>
       <c r="O59">
-        <v>0.4718220840000001</v>
+        <v>0.4692522960000001</v>
       </c>
       <c r="P59">
-        <v>1.100918196</v>
+        <v>1.094922024</v>
       </c>
       <c r="Q59">
-        <v>1.259918196</v>
+        <v>1.253922024</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.3201714605088632</v>
+        <v>0.3256875735066289</v>
       </c>
       <c r="T59">
-        <v>1.913039247087284</v>
+        <v>1.951500028090245</v>
       </c>
       <c r="U59">
         <v>0.0578</v>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>4.221114123442335</v>
+        <v>4.148336293727812</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.1602555808727841</v>
+        <v>0.1597752337267571</v>
       </c>
       <c r="C60">
-        <v>9.11794032422309</v>
+        <v>9.030991741641952</v>
       </c>
       <c r="D60">
-        <v>14.53354032422309</v>
+        <v>14.59479174164195</v>
       </c>
       <c r="E60">
-        <v>6.375599999999999</v>
+        <v>6.5238</v>
       </c>
       <c r="F60">
-        <v>8.595599999999999</v>
+        <v>8.7438</v>
       </c>
       <c r="G60">
         <v>3.18</v>
@@ -6201,28 +6201,28 @@
         <v>2.061</v>
       </c>
       <c r="M60">
-        <v>0.49682568</v>
+        <v>0.50539164</v>
       </c>
       <c r="N60">
-        <v>1.56417432</v>
+        <v>1.55560836</v>
       </c>
       <c r="O60">
-        <v>0.4692522960000001</v>
+        <v>0.4666825080000001</v>
       </c>
       <c r="P60">
-        <v>1.094922024</v>
+        <v>1.088925852</v>
       </c>
       <c r="Q60">
-        <v>1.253922024</v>
+        <v>1.247925852</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.3256875735066289</v>
+        <v>0.3314727651872123</v>
       </c>
       <c r="T60">
-        <v>1.951500028090245</v>
+        <v>1.991836944751887</v>
       </c>
       <c r="U60">
         <v>0.0578</v>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>4.148336293727813</v>
+        <v>4.078025509088358</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.1597752337267571</v>
+        <v>0.15929488658073</v>
       </c>
       <c r="C61">
-        <v>9.030991741641952</v>
+        <v>8.94456163076352</v>
       </c>
       <c r="D61">
-        <v>14.59479174164195</v>
+        <v>14.65656163076352</v>
       </c>
       <c r="E61">
-        <v>6.5238</v>
+        <v>6.671999999999999</v>
       </c>
       <c r="F61">
-        <v>8.7438</v>
+        <v>8.891999999999999</v>
       </c>
       <c r="G61">
         <v>3.18</v>
@@ -6283,28 +6283,28 @@
         <v>2.061</v>
       </c>
       <c r="M61">
-        <v>0.50539164</v>
+        <v>0.5139576</v>
       </c>
       <c r="N61">
-        <v>1.55560836</v>
+        <v>1.5470424</v>
       </c>
       <c r="O61">
-        <v>0.4666825080000001</v>
+        <v>0.4641127200000001</v>
       </c>
       <c r="P61">
-        <v>1.088925852</v>
+        <v>1.08292968</v>
       </c>
       <c r="Q61">
-        <v>1.247925852</v>
+        <v>1.24192968</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.3314727651872123</v>
+        <v>0.337547216451825</v>
       </c>
       <c r="T61">
-        <v>1.991836944751887</v>
+        <v>2.034190707246611</v>
       </c>
       <c r="U61">
         <v>0.0578</v>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.078025509088358</v>
+        <v>4.010058417270219</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.15929488658073</v>
+        <v>0.160309039434703</v>
       </c>
       <c r="C62">
-        <v>8.94456163076352</v>
+        <v>8.666555338783004</v>
       </c>
       <c r="D62">
-        <v>14.65656163076352</v>
+        <v>14.526755338783</v>
       </c>
       <c r="E62">
-        <v>6.671999999999999</v>
+        <v>6.8202</v>
       </c>
       <c r="F62">
-        <v>8.891999999999999</v>
+        <v>9.0402</v>
       </c>
       <c r="G62">
         <v>3.18</v>
@@ -6365,45 +6365,45 @@
         <v>2.061</v>
       </c>
       <c r="M62">
-        <v>0.5139576</v>
+        <v>0.5541642600000001</v>
       </c>
       <c r="N62">
-        <v>1.5470424</v>
+        <v>1.50683574</v>
       </c>
       <c r="O62">
-        <v>0.4641127200000001</v>
+        <v>0.4520507220000001</v>
       </c>
       <c r="P62">
-        <v>1.08292968</v>
+        <v>1.054785018</v>
       </c>
       <c r="Q62">
-        <v>1.24192968</v>
+        <v>1.213785018</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.337547216451825</v>
+        <v>0.3439331780376998</v>
       </c>
       <c r="T62">
-        <v>2.034190707246611</v>
+        <v>2.078716457561578</v>
       </c>
       <c r="U62">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V62">
         <v>0.3</v>
       </c>
       <c r="W62">
-        <v>0.04046</v>
+        <v>0.04291</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y62">
-        <v>4.010058417270219</v>
+        <v>3.719113895941251</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.160309039434703</v>
+        <v>0.1598531922886759</v>
       </c>
       <c r="C63">
-        <v>8.666555338783004</v>
+        <v>8.576415791360754</v>
       </c>
       <c r="D63">
-        <v>14.526755338783</v>
+        <v>14.58481579136075</v>
       </c>
       <c r="E63">
-        <v>6.8202</v>
+        <v>6.968399999999999</v>
       </c>
       <c r="F63">
-        <v>9.0402</v>
+        <v>9.1884</v>
       </c>
       <c r="G63">
         <v>3.18</v>
@@ -6447,28 +6447,28 @@
         <v>2.061</v>
       </c>
       <c r="M63">
-        <v>0.5541642600000001</v>
+        <v>0.5632489199999999</v>
       </c>
       <c r="N63">
-        <v>1.50683574</v>
+        <v>1.49775108</v>
       </c>
       <c r="O63">
-        <v>0.4520507220000001</v>
+        <v>0.4493253240000001</v>
       </c>
       <c r="P63">
-        <v>1.054785018</v>
+        <v>1.048425756</v>
       </c>
       <c r="Q63">
-        <v>1.213785018</v>
+        <v>1.207425756</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.3439331780376998</v>
+        <v>0.3506552428649365</v>
       </c>
       <c r="T63">
-        <v>2.078716457561578</v>
+        <v>2.125585668419437</v>
       </c>
       <c r="U63">
         <v>0.0613</v>
@@ -6485,7 +6485,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>3.719113895941251</v>
+        <v>3.659128187942199</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.1598531922886759</v>
+        <v>0.1593973451426488</v>
       </c>
       <c r="C64">
-        <v>8.576415791360754</v>
+        <v>8.486742217708777</v>
       </c>
       <c r="D64">
-        <v>14.58481579136075</v>
+        <v>14.64334221770878</v>
       </c>
       <c r="E64">
-        <v>6.968399999999999</v>
+        <v>7.1166</v>
       </c>
       <c r="F64">
-        <v>9.1884</v>
+        <v>9.336600000000001</v>
       </c>
       <c r="G64">
         <v>3.18</v>
@@ -6529,28 +6529,28 @@
         <v>2.061</v>
       </c>
       <c r="M64">
-        <v>0.5632489199999999</v>
+        <v>0.57233358</v>
       </c>
       <c r="N64">
-        <v>1.49775108</v>
+        <v>1.48866642</v>
       </c>
       <c r="O64">
-        <v>0.4493253240000001</v>
+        <v>0.4465999260000001</v>
       </c>
       <c r="P64">
-        <v>1.048425756</v>
+        <v>1.042066494</v>
       </c>
       <c r="Q64">
-        <v>1.207425756</v>
+        <v>1.201066494</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3506552428649365</v>
+        <v>0.3577406625476995</v>
       </c>
       <c r="T64">
-        <v>2.125585668419437</v>
+        <v>2.174988350134478</v>
       </c>
       <c r="U64">
         <v>0.0613</v>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>3.659128187942199</v>
+        <v>3.601046788133592</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.1593973451426488</v>
+        <v>0.1589414979966218</v>
       </c>
       <c r="C65">
-        <v>8.486742217708777</v>
+        <v>8.397540250052661</v>
       </c>
       <c r="D65">
-        <v>14.64334221770878</v>
+        <v>14.70234025005266</v>
       </c>
       <c r="E65">
-        <v>7.1166</v>
+        <v>7.264799999999999</v>
       </c>
       <c r="F65">
-        <v>9.336600000000001</v>
+        <v>9.4848</v>
       </c>
       <c r="G65">
         <v>3.18</v>
@@ -6611,28 +6611,28 @@
         <v>2.061</v>
       </c>
       <c r="M65">
-        <v>0.57233358</v>
+        <v>0.58141824</v>
       </c>
       <c r="N65">
-        <v>1.48866642</v>
+        <v>1.47958176</v>
       </c>
       <c r="O65">
-        <v>0.4465999260000001</v>
+        <v>0.4438745280000001</v>
       </c>
       <c r="P65">
-        <v>1.042066494</v>
+        <v>1.035707232</v>
       </c>
       <c r="Q65">
-        <v>1.201066494</v>
+        <v>1.194707232</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3577406625476995</v>
+        <v>0.3652197166572827</v>
       </c>
       <c r="T65">
-        <v>2.174988350134478</v>
+        <v>2.227135625278133</v>
       </c>
       <c r="U65">
         <v>0.0613</v>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>3.601046788133592</v>
+        <v>3.544780432069005</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.1589414979966218</v>
+        <v>0.1597596508505947</v>
       </c>
       <c r="C66">
-        <v>8.397540250052661</v>
+        <v>8.143787437755686</v>
       </c>
       <c r="D66">
-        <v>14.70234025005266</v>
+        <v>14.59678743775568</v>
       </c>
       <c r="E66">
-        <v>7.264799999999999</v>
+        <v>7.413</v>
       </c>
       <c r="F66">
-        <v>9.4848</v>
+        <v>9.633000000000001</v>
       </c>
       <c r="G66">
         <v>3.18</v>
@@ -6693,45 +6693,45 @@
         <v>2.061</v>
       </c>
       <c r="M66">
-        <v>0.58141824</v>
+        <v>0.6174753000000001</v>
       </c>
       <c r="N66">
-        <v>1.47958176</v>
+        <v>1.4435247</v>
       </c>
       <c r="O66">
-        <v>0.4438745280000001</v>
+        <v>0.43305741</v>
       </c>
       <c r="P66">
-        <v>1.035707232</v>
+        <v>1.01046729</v>
       </c>
       <c r="Q66">
-        <v>1.194707232</v>
+        <v>1.16946729</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.3652197166572827</v>
+        <v>0.3731261452874134</v>
       </c>
       <c r="T66">
-        <v>2.227135625278133</v>
+        <v>2.28226274471571</v>
       </c>
       <c r="U66">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V66">
         <v>0.3</v>
       </c>
       <c r="W66">
-        <v>0.04291</v>
+        <v>0.04487</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>3.544780432069005</v>
+        <v>3.337785333275679</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1597596508505947</v>
+        <v>0.1593234037045677</v>
       </c>
       <c r="C67">
-        <v>8.143787437755686</v>
+        <v>8.051679896694425</v>
       </c>
       <c r="D67">
-        <v>14.59678743775568</v>
+        <v>14.65287989669443</v>
       </c>
       <c r="E67">
-        <v>7.413</v>
+        <v>7.561199999999999</v>
       </c>
       <c r="F67">
-        <v>9.633000000000001</v>
+        <v>9.7812</v>
       </c>
       <c r="G67">
         <v>3.18</v>
@@ -6775,28 +6775,28 @@
         <v>2.061</v>
       </c>
       <c r="M67">
-        <v>0.6174753000000001</v>
+        <v>0.6269749200000001</v>
       </c>
       <c r="N67">
-        <v>1.4435247</v>
+        <v>1.43402508</v>
       </c>
       <c r="O67">
-        <v>0.43305741</v>
+        <v>0.4302075240000001</v>
       </c>
       <c r="P67">
-        <v>1.01046729</v>
+        <v>1.003817556</v>
       </c>
       <c r="Q67">
-        <v>1.16946729</v>
+        <v>1.162817556</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3731261452874134</v>
+        <v>0.3814976579546108</v>
       </c>
       <c r="T67">
-        <v>2.28226274471571</v>
+        <v>2.34063263588491</v>
       </c>
       <c r="U67">
         <v>0.0641</v>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>3.337785333275679</v>
+        <v>3.287212828226048</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1593234037045677</v>
+        <v>0.1588871565585406</v>
       </c>
       <c r="C68">
-        <v>8.051679896694425</v>
+        <v>7.960005122286258</v>
       </c>
       <c r="D68">
-        <v>14.65287989669443</v>
+        <v>14.70940512228626</v>
       </c>
       <c r="E68">
-        <v>7.561199999999999</v>
+        <v>7.7094</v>
       </c>
       <c r="F68">
-        <v>9.7812</v>
+        <v>9.929400000000001</v>
       </c>
       <c r="G68">
         <v>3.18</v>
@@ -6857,28 +6857,28 @@
         <v>2.061</v>
       </c>
       <c r="M68">
-        <v>0.6269749200000001</v>
+        <v>0.6364745400000001</v>
       </c>
       <c r="N68">
-        <v>1.43402508</v>
+        <v>1.42452546</v>
       </c>
       <c r="O68">
-        <v>0.4302075240000001</v>
+        <v>0.4273576380000001</v>
       </c>
       <c r="P68">
-        <v>1.003817556</v>
+        <v>0.9971678220000002</v>
       </c>
       <c r="Q68">
-        <v>1.162817556</v>
+        <v>1.156167822</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.3814976579546108</v>
+        <v>0.3903765350258806</v>
       </c>
       <c r="T68">
-        <v>2.34063263588491</v>
+        <v>2.40254009621588</v>
       </c>
       <c r="U68">
         <v>0.0641</v>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>3.287212828226048</v>
+        <v>3.238149950192823</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1588871565585406</v>
+        <v>0.1584509094125135</v>
       </c>
       <c r="C69">
-        <v>7.960005122286258</v>
+        <v>7.868768142272678</v>
       </c>
       <c r="D69">
-        <v>14.70940512228626</v>
+        <v>14.76636814227268</v>
       </c>
       <c r="E69">
-        <v>7.7094</v>
+        <v>7.8576</v>
       </c>
       <c r="F69">
-        <v>9.929400000000001</v>
+        <v>10.0776</v>
       </c>
       <c r="G69">
         <v>3.18</v>
@@ -6939,28 +6939,28 @@
         <v>2.061</v>
       </c>
       <c r="M69">
-        <v>0.6364745400000001</v>
+        <v>0.6459741600000001</v>
       </c>
       <c r="N69">
-        <v>1.42452546</v>
+        <v>1.41502584</v>
       </c>
       <c r="O69">
-        <v>0.4273576380000001</v>
+        <v>0.4245077520000001</v>
       </c>
       <c r="P69">
-        <v>0.9971678220000002</v>
+        <v>0.9905180880000002</v>
       </c>
       <c r="Q69">
-        <v>1.156167822</v>
+        <v>1.149518088</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3903765350258806</v>
+        <v>0.3998103419141048</v>
       </c>
       <c r="T69">
-        <v>2.40254009621588</v>
+        <v>2.468316772817535</v>
       </c>
       <c r="U69">
         <v>0.0641</v>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>3.238149950192823</v>
+        <v>3.190530097984105</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1584509094125135</v>
+        <v>0.1580146622664864</v>
       </c>
       <c r="C70">
-        <v>7.868768142272678</v>
+        <v>7.777974062578826</v>
       </c>
       <c r="D70">
-        <v>14.76636814227268</v>
+        <v>14.82377406257883</v>
       </c>
       <c r="E70">
-        <v>7.8576</v>
+        <v>8.005800000000001</v>
       </c>
       <c r="F70">
-        <v>10.0776</v>
+        <v>10.2258</v>
       </c>
       <c r="G70">
         <v>3.18</v>
@@ -7021,28 +7021,28 @@
         <v>2.061</v>
       </c>
       <c r="M70">
-        <v>0.6459741600000001</v>
+        <v>0.6554737800000001</v>
       </c>
       <c r="N70">
-        <v>1.41502584</v>
+        <v>1.40552622</v>
       </c>
       <c r="O70">
-        <v>0.4245077520000001</v>
+        <v>0.421657866</v>
       </c>
       <c r="P70">
-        <v>0.9905180880000002</v>
+        <v>0.9838683540000002</v>
       </c>
       <c r="Q70">
-        <v>1.149518088</v>
+        <v>1.142868354</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3998103419141048</v>
+        <v>0.4098527815047951</v>
       </c>
       <c r="T70">
-        <v>2.468316772817535</v>
+        <v>2.538337105974136</v>
       </c>
       <c r="U70">
         <v>0.0641</v>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>3.190530097984105</v>
+        <v>3.144290531346654</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1580146622664864</v>
+        <v>0.1575784151204594</v>
       </c>
       <c r="C71">
-        <v>7.777974062578826</v>
+        <v>7.687628068839166</v>
       </c>
       <c r="D71">
-        <v>14.82377406257883</v>
+        <v>14.88162806883917</v>
       </c>
       <c r="E71">
-        <v>8.005800000000001</v>
+        <v>8.154</v>
       </c>
       <c r="F71">
-        <v>10.2258</v>
+        <v>10.374</v>
       </c>
       <c r="G71">
         <v>3.18</v>
@@ -7103,28 +7103,28 @@
         <v>2.061</v>
       </c>
       <c r="M71">
-        <v>0.6554737800000001</v>
+        <v>0.6649734</v>
       </c>
       <c r="N71">
-        <v>1.40552622</v>
+        <v>1.3960266</v>
       </c>
       <c r="O71">
-        <v>0.421657866</v>
+        <v>0.4188079800000001</v>
       </c>
       <c r="P71">
-        <v>0.9838683540000002</v>
+        <v>0.9772186200000003</v>
       </c>
       <c r="Q71">
-        <v>1.142868354</v>
+        <v>1.13621862</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.4098527815047951</v>
+        <v>0.420564717068198</v>
       </c>
       <c r="T71">
-        <v>2.538337105974136</v>
+        <v>2.613025461341176</v>
       </c>
       <c r="U71">
         <v>0.0641</v>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>3.144290531346654</v>
+        <v>3.09937209518456</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1575784151204594</v>
+        <v>0.1571421679744323</v>
       </c>
       <c r="C72">
-        <v>7.687628068839166</v>
+        <v>7.597735427959012</v>
       </c>
       <c r="D72">
-        <v>14.88162806883917</v>
+        <v>14.93993542795901</v>
       </c>
       <c r="E72">
-        <v>8.154</v>
+        <v>8.302200000000001</v>
       </c>
       <c r="F72">
-        <v>10.374</v>
+        <v>10.5222</v>
       </c>
       <c r="G72">
         <v>3.18</v>
@@ -7185,28 +7185,28 @@
         <v>2.061</v>
       </c>
       <c r="M72">
-        <v>0.6649734</v>
+        <v>0.6744730200000001</v>
       </c>
       <c r="N72">
-        <v>1.3960266</v>
+        <v>1.38652698</v>
       </c>
       <c r="O72">
-        <v>0.4188079800000001</v>
+        <v>0.4159580940000001</v>
       </c>
       <c r="P72">
-        <v>0.9772186200000003</v>
+        <v>0.9705688860000001</v>
       </c>
       <c r="Q72">
-        <v>1.13621862</v>
+        <v>1.129568886</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.420564717068198</v>
+        <v>0.4320154068083875</v>
       </c>
       <c r="T72">
-        <v>2.613025461341176</v>
+        <v>2.692864737768013</v>
       </c>
       <c r="U72">
         <v>0.0641</v>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.09937209518456</v>
+        <v>3.055718967083368</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1571421679744323</v>
+        <v>0.1567059208284053</v>
       </c>
       <c r="C73">
-        <v>7.597735427959011</v>
+        <v>7.508301489712915</v>
       </c>
       <c r="D73">
-        <v>14.93993542795901</v>
+        <v>14.99870148971291</v>
       </c>
       <c r="E73">
-        <v>8.302199999999999</v>
+        <v>8.450399999999998</v>
       </c>
       <c r="F73">
-        <v>10.5222</v>
+        <v>10.6704</v>
       </c>
       <c r="G73">
         <v>3.18</v>
@@ -7267,28 +7267,28 @@
         <v>2.061</v>
       </c>
       <c r="M73">
-        <v>0.67447302</v>
+        <v>0.68397264</v>
       </c>
       <c r="N73">
-        <v>1.38652698</v>
+        <v>1.37702736</v>
       </c>
       <c r="O73">
-        <v>0.4159580940000001</v>
+        <v>0.4131082080000001</v>
       </c>
       <c r="P73">
-        <v>0.9705688860000004</v>
+        <v>0.9639191520000003</v>
       </c>
       <c r="Q73">
-        <v>1.129568886</v>
+        <v>1.122919152</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.4320154068083873</v>
+        <v>0.4442840029585903</v>
       </c>
       <c r="T73">
-        <v>2.692864737768012</v>
+        <v>2.778406819653908</v>
       </c>
       <c r="U73">
         <v>0.0641</v>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.055718967083369</v>
+        <v>3.013278425873878</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1567059208284053</v>
+        <v>0.1602554736823782</v>
       </c>
       <c r="C74">
-        <v>7.508301489712915</v>
+        <v>6.894953935246104</v>
       </c>
       <c r="D74">
-        <v>14.99870148971291</v>
+        <v>14.5335539352461</v>
       </c>
       <c r="E74">
-        <v>8.450399999999998</v>
+        <v>8.598599999999999</v>
       </c>
       <c r="F74">
-        <v>10.6704</v>
+        <v>10.8186</v>
       </c>
       <c r="G74">
         <v>3.18</v>
@@ -7349,45 +7349,45 @@
         <v>2.061</v>
       </c>
       <c r="M74">
-        <v>0.68397264</v>
+        <v>0.7778573400000001</v>
       </c>
       <c r="N74">
-        <v>1.37702736</v>
+        <v>1.28314266</v>
       </c>
       <c r="O74">
-        <v>0.4131082080000001</v>
+        <v>0.384942798</v>
       </c>
       <c r="P74">
-        <v>0.9639191520000003</v>
+        <v>0.8981998620000002</v>
       </c>
       <c r="Q74">
-        <v>1.122919152</v>
+        <v>1.057199862</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4442840029585903</v>
+        <v>0.4574613840088082</v>
       </c>
       <c r="T74">
-        <v>2.778406819653908</v>
+        <v>2.870285352049871</v>
       </c>
       <c r="U74">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V74">
         <v>0.3</v>
       </c>
       <c r="W74">
-        <v>0.04487</v>
+        <v>0.05033</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y74">
-        <v>3.013278425873878</v>
+        <v>2.649586105339059</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1602554736823782</v>
+        <v>0.1598738265363512</v>
       </c>
       <c r="C75">
-        <v>6.894953935246104</v>
+        <v>6.79537761650089</v>
       </c>
       <c r="D75">
-        <v>14.5335539352461</v>
+        <v>14.58217761650089</v>
       </c>
       <c r="E75">
-        <v>8.598599999999999</v>
+        <v>8.746799999999999</v>
       </c>
       <c r="F75">
-        <v>10.8186</v>
+        <v>10.9668</v>
       </c>
       <c r="G75">
         <v>3.18</v>
@@ -7431,28 +7431,28 @@
         <v>2.061</v>
       </c>
       <c r="M75">
-        <v>0.7778573400000001</v>
+        <v>0.78851292</v>
       </c>
       <c r="N75">
-        <v>1.28314266</v>
+        <v>1.27248708</v>
       </c>
       <c r="O75">
-        <v>0.384942798</v>
+        <v>0.3817461240000001</v>
       </c>
       <c r="P75">
-        <v>0.8981998620000002</v>
+        <v>0.8907409560000003</v>
       </c>
       <c r="Q75">
-        <v>1.057199862</v>
+        <v>1.049740956</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4574613840088082</v>
+        <v>0.4716524097551967</v>
       </c>
       <c r="T75">
-        <v>2.870285352049871</v>
+        <v>2.969231463860907</v>
       </c>
       <c r="U75">
         <v>0.07190000000000001</v>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>2.649586105339059</v>
+        <v>2.613780887699342</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1598738265363512</v>
+        <v>0.1594921793903241</v>
       </c>
       <c r="C76">
-        <v>6.79537761650089</v>
+        <v>6.696127742182723</v>
       </c>
       <c r="D76">
-        <v>14.58217761650089</v>
+        <v>14.63112774218272</v>
       </c>
       <c r="E76">
-        <v>8.746799999999999</v>
+        <v>8.895</v>
       </c>
       <c r="F76">
-        <v>10.9668</v>
+        <v>11.115</v>
       </c>
       <c r="G76">
         <v>3.18</v>
@@ -7513,28 +7513,28 @@
         <v>2.061</v>
       </c>
       <c r="M76">
-        <v>0.78851292</v>
+        <v>0.7991685000000001</v>
       </c>
       <c r="N76">
-        <v>1.27248708</v>
+        <v>1.2618315</v>
       </c>
       <c r="O76">
-        <v>0.3817461240000001</v>
+        <v>0.3785494500000001</v>
       </c>
       <c r="P76">
-        <v>0.8907409560000003</v>
+        <v>0.8832820500000003</v>
       </c>
       <c r="Q76">
-        <v>1.049740956</v>
+        <v>1.04228205</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4716524097551967</v>
+        <v>0.4869787175612963</v>
       </c>
       <c r="T76">
-        <v>2.969231463860907</v>
+        <v>3.076093264616826</v>
       </c>
       <c r="U76">
         <v>0.07190000000000001</v>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>2.613780887699342</v>
+        <v>2.578930475863351</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1594921793903241</v>
+        <v>0.1591105322442971</v>
       </c>
       <c r="C77">
-        <v>6.696127742182723</v>
+        <v>6.597207610835365</v>
       </c>
       <c r="D77">
-        <v>14.63112774218272</v>
+        <v>14.68040761083537</v>
       </c>
       <c r="E77">
-        <v>8.895</v>
+        <v>9.043200000000001</v>
       </c>
       <c r="F77">
-        <v>11.115</v>
+        <v>11.2632</v>
       </c>
       <c r="G77">
         <v>3.18</v>
@@ -7595,28 +7595,28 @@
         <v>2.061</v>
       </c>
       <c r="M77">
-        <v>0.7991685000000001</v>
+        <v>0.8098240800000002</v>
       </c>
       <c r="N77">
-        <v>1.2618315</v>
+        <v>1.25117592</v>
       </c>
       <c r="O77">
-        <v>0.3785494500000001</v>
+        <v>0.375352776</v>
       </c>
       <c r="P77">
-        <v>0.8832820500000003</v>
+        <v>0.8758231440000002</v>
       </c>
       <c r="Q77">
-        <v>1.04228205</v>
+        <v>1.034823144</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4869787175612963</v>
+        <v>0.503582217684571</v>
       </c>
       <c r="T77">
-        <v>3.076093264616826</v>
+        <v>3.19186021543574</v>
       </c>
       <c r="U77">
         <v>0.07190000000000001</v>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>2.578930475863351</v>
+        <v>2.544997180128306</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1591105322442971</v>
+        <v>0.15872888509827</v>
       </c>
       <c r="C78">
-        <v>6.597207610835365</v>
+        <v>6.498620565592816</v>
       </c>
       <c r="D78">
-        <v>14.68040761083537</v>
+        <v>14.73002056559282</v>
       </c>
       <c r="E78">
-        <v>9.043200000000001</v>
+        <v>9.1914</v>
       </c>
       <c r="F78">
-        <v>11.2632</v>
+        <v>11.4114</v>
       </c>
       <c r="G78">
         <v>3.18</v>
@@ -7677,28 +7677,28 @@
         <v>2.061</v>
       </c>
       <c r="M78">
-        <v>0.8098240800000002</v>
+        <v>0.8204796600000001</v>
       </c>
       <c r="N78">
-        <v>1.25117592</v>
+        <v>1.24052034</v>
       </c>
       <c r="O78">
-        <v>0.375352776</v>
+        <v>0.372156102</v>
       </c>
       <c r="P78">
-        <v>0.8758231440000002</v>
+        <v>0.8683642380000002</v>
       </c>
       <c r="Q78">
-        <v>1.034823144</v>
+        <v>1.027364238</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.503582217684571</v>
+        <v>0.5216295004272608</v>
       </c>
       <c r="T78">
-        <v>3.19186021543574</v>
+        <v>3.31769385763021</v>
       </c>
       <c r="U78">
         <v>0.07190000000000001</v>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>2.544997180128306</v>
+        <v>2.511945268698069</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.15872888509827</v>
+        <v>0.1604766379522429</v>
       </c>
       <c r="C79">
-        <v>6.498620565592816</v>
+        <v>6.125924661786188</v>
       </c>
       <c r="D79">
-        <v>14.73002056559282</v>
+        <v>14.50552466178619</v>
       </c>
       <c r="E79">
-        <v>9.1914</v>
+        <v>9.339600000000001</v>
       </c>
       <c r="F79">
-        <v>11.4114</v>
+        <v>11.5596</v>
       </c>
       <c r="G79">
         <v>3.18</v>
@@ -7759,45 +7759,45 @@
         <v>2.061</v>
       </c>
       <c r="M79">
-        <v>0.8204796600000001</v>
+        <v>0.8762176800000002</v>
       </c>
       <c r="N79">
-        <v>1.24052034</v>
+        <v>1.18478232</v>
       </c>
       <c r="O79">
-        <v>0.372156102</v>
+        <v>0.355434696</v>
       </c>
       <c r="P79">
-        <v>0.8683642380000002</v>
+        <v>0.8293476240000001</v>
       </c>
       <c r="Q79">
-        <v>1.027364238</v>
+        <v>0.9883476240000001</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.5216295004272608</v>
+        <v>0.5413174452374677</v>
       </c>
       <c r="T79">
-        <v>3.31769385763021</v>
+        <v>3.45496692184236</v>
       </c>
       <c r="U79">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V79">
         <v>0.3</v>
       </c>
       <c r="W79">
-        <v>0.05033</v>
+        <v>0.05306</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y79">
-        <v>2.511945268698069</v>
+        <v>2.352155231563006</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1604766379522429</v>
+        <v>0.1601222908062158</v>
       </c>
       <c r="C80">
-        <v>6.125924661786188</v>
+        <v>6.022685195985433</v>
       </c>
       <c r="D80">
-        <v>14.50552466178619</v>
+        <v>14.55048519598543</v>
       </c>
       <c r="E80">
-        <v>9.339600000000001</v>
+        <v>9.4878</v>
       </c>
       <c r="F80">
-        <v>11.5596</v>
+        <v>11.7078</v>
       </c>
       <c r="G80">
         <v>3.18</v>
@@ -7841,28 +7841,28 @@
         <v>2.061</v>
       </c>
       <c r="M80">
-        <v>0.8762176800000002</v>
+        <v>0.8874512400000001</v>
       </c>
       <c r="N80">
-        <v>1.18478232</v>
+        <v>1.17354876</v>
       </c>
       <c r="O80">
-        <v>0.355434696</v>
+        <v>0.3520646280000001</v>
       </c>
       <c r="P80">
-        <v>0.8293476240000001</v>
+        <v>0.8214841320000001</v>
       </c>
       <c r="Q80">
-        <v>0.9883476240000001</v>
+        <v>0.9804841320000002</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5413174452374677</v>
+        <v>0.5628804324105516</v>
       </c>
       <c r="T80">
-        <v>3.45496692184236</v>
+        <v>3.605313611217572</v>
       </c>
       <c r="U80">
         <v>0.07580000000000001</v>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>2.352155231563006</v>
+        <v>2.322381114707778</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1601222908062158</v>
+        <v>0.1597679436601888</v>
       </c>
       <c r="C81">
-        <v>6.022685195985433</v>
+        <v>5.919725311204846</v>
       </c>
       <c r="D81">
-        <v>14.55048519598543</v>
+        <v>14.59572531120485</v>
       </c>
       <c r="E81">
-        <v>9.4878</v>
+        <v>9.636000000000001</v>
       </c>
       <c r="F81">
-        <v>11.7078</v>
+        <v>11.856</v>
       </c>
       <c r="G81">
         <v>3.18</v>
@@ -7923,28 +7923,28 @@
         <v>2.061</v>
       </c>
       <c r="M81">
-        <v>0.8874512400000001</v>
+        <v>0.8986848000000002</v>
       </c>
       <c r="N81">
-        <v>1.17354876</v>
+        <v>1.1623152</v>
       </c>
       <c r="O81">
-        <v>0.3520646280000001</v>
+        <v>0.34869456</v>
       </c>
       <c r="P81">
-        <v>0.8214841320000001</v>
+        <v>0.8136206400000001</v>
       </c>
       <c r="Q81">
-        <v>0.9804841320000002</v>
+        <v>0.9726206400000001</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5628804324105516</v>
+        <v>0.5865997183009439</v>
       </c>
       <c r="T81">
-        <v>3.605313611217572</v>
+        <v>3.770694969530304</v>
       </c>
       <c r="U81">
         <v>0.07580000000000001</v>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>2.322381114707778</v>
+        <v>2.293351350773931</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1597679436601888</v>
+        <v>0.1594135965141617</v>
       </c>
       <c r="C82">
-        <v>5.919725311204846</v>
+        <v>5.817047623383175</v>
       </c>
       <c r="D82">
-        <v>14.59572531120485</v>
+        <v>14.64124762338317</v>
       </c>
       <c r="E82">
-        <v>9.636000000000001</v>
+        <v>9.7842</v>
       </c>
       <c r="F82">
-        <v>11.856</v>
+        <v>12.0042</v>
       </c>
       <c r="G82">
         <v>3.18</v>
@@ -8005,28 +8005,28 @@
         <v>2.061</v>
       </c>
       <c r="M82">
-        <v>0.8986848000000002</v>
+        <v>0.9099183600000001</v>
       </c>
       <c r="N82">
-        <v>1.1623152</v>
+        <v>1.15108164</v>
       </c>
       <c r="O82">
-        <v>0.34869456</v>
+        <v>0.345324492</v>
       </c>
       <c r="P82">
-        <v>0.8136206400000001</v>
+        <v>0.8057571480000001</v>
       </c>
       <c r="Q82">
-        <v>0.9726206400000001</v>
+        <v>0.9647571480000001</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5865997183009439</v>
+        <v>0.612815771127167</v>
       </c>
       <c r="T82">
-        <v>3.770694969530304</v>
+        <v>3.953484891875957</v>
       </c>
       <c r="U82">
         <v>0.07580000000000001</v>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>2.293351350773931</v>
+        <v>2.265038371134747</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.1594135965141617</v>
+        <v>0.1590592493681347</v>
       </c>
       <c r="C83">
-        <v>5.817047623383175</v>
+        <v>5.714654781196463</v>
       </c>
       <c r="D83">
-        <v>14.64124762338317</v>
+        <v>14.68705478119646</v>
       </c>
       <c r="E83">
-        <v>9.7842</v>
+        <v>9.932400000000001</v>
       </c>
       <c r="F83">
-        <v>12.0042</v>
+        <v>12.1524</v>
       </c>
       <c r="G83">
         <v>3.18</v>
@@ -8087,28 +8087,28 @@
         <v>2.061</v>
       </c>
       <c r="M83">
-        <v>0.9099183600000001</v>
+        <v>0.9211519200000002</v>
       </c>
       <c r="N83">
-        <v>1.15108164</v>
+        <v>1.13984808</v>
       </c>
       <c r="O83">
-        <v>0.345324492</v>
+        <v>0.341954424</v>
       </c>
       <c r="P83">
-        <v>0.8057571480000001</v>
+        <v>0.7978936560000001</v>
       </c>
       <c r="Q83">
-        <v>0.9647571480000001</v>
+        <v>0.9568936560000001</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.612815771127167</v>
+        <v>0.6419447187118594</v>
       </c>
       <c r="T83">
-        <v>3.953484891875957</v>
+        <v>4.156584805593348</v>
       </c>
       <c r="U83">
         <v>0.07580000000000001</v>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>2.265038371134747</v>
+        <v>2.237415951974567</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.1590592493681347</v>
+        <v>0.1587049022221076</v>
       </c>
       <c r="C84">
-        <v>5.714654781196463</v>
+        <v>5.612549466571791</v>
       </c>
       <c r="D84">
-        <v>14.68705478119646</v>
+        <v>14.73314946657179</v>
       </c>
       <c r="E84">
-        <v>9.932400000000001</v>
+        <v>10.0806</v>
       </c>
       <c r="F84">
-        <v>12.1524</v>
+        <v>12.3006</v>
       </c>
       <c r="G84">
         <v>3.18</v>
@@ -8169,28 +8169,28 @@
         <v>2.061</v>
       </c>
       <c r="M84">
-        <v>0.9211519200000002</v>
+        <v>0.9323854800000002</v>
       </c>
       <c r="N84">
-        <v>1.13984808</v>
+        <v>1.12861452</v>
       </c>
       <c r="O84">
-        <v>0.341954424</v>
+        <v>0.338584356</v>
       </c>
       <c r="P84">
-        <v>0.7978936560000001</v>
+        <v>0.7900301640000001</v>
       </c>
       <c r="Q84">
-        <v>0.9568936560000001</v>
+        <v>0.9490301640000002</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.6419447187118594</v>
+        <v>0.6745006013065155</v>
       </c>
       <c r="T84">
-        <v>4.156584805593348</v>
+        <v>4.383578826806903</v>
       </c>
       <c r="U84">
         <v>0.07580000000000001</v>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>2.237415951974567</v>
+        <v>2.210459133276078</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.1587049022221076</v>
+        <v>0.1583505550760805</v>
       </c>
       <c r="C85">
-        <v>5.612549466571791</v>
+        <v>5.510734395210665</v>
       </c>
       <c r="D85">
-        <v>14.73314946657179</v>
+        <v>14.77953439521067</v>
       </c>
       <c r="E85">
-        <v>10.0806</v>
+        <v>10.2288</v>
       </c>
       <c r="F85">
-        <v>12.3006</v>
+        <v>12.4488</v>
       </c>
       <c r="G85">
         <v>3.18</v>
@@ -8251,28 +8251,28 @@
         <v>2.061</v>
       </c>
       <c r="M85">
-        <v>0.9323854800000002</v>
+        <v>0.9436190400000002</v>
       </c>
       <c r="N85">
-        <v>1.12861452</v>
+        <v>1.11738096</v>
       </c>
       <c r="O85">
-        <v>0.338584356</v>
+        <v>0.335214288</v>
       </c>
       <c r="P85">
-        <v>0.7900301640000001</v>
+        <v>0.7821666720000002</v>
       </c>
       <c r="Q85">
-        <v>0.9490301640000002</v>
+        <v>0.9411666720000003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.6745006013065155</v>
+        <v>0.7111259692255038</v>
       </c>
       <c r="T85">
-        <v>4.383578826806903</v>
+        <v>4.638947100672153</v>
       </c>
       <c r="U85">
         <v>0.07580000000000001</v>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>2.210459133276078</v>
+        <v>2.18414414359422</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.1583505550760806</v>
+        <v>0.1579962079300535</v>
       </c>
       <c r="C86">
-        <v>5.510734395210664</v>
+        <v>5.409212317122401</v>
       </c>
       <c r="D86">
-        <v>14.77953439521066</v>
+        <v>14.8262123171224</v>
       </c>
       <c r="E86">
-        <v>10.2288</v>
+        <v>10.377</v>
       </c>
       <c r="F86">
-        <v>12.4488</v>
+        <v>12.597</v>
       </c>
       <c r="G86">
         <v>3.18</v>
@@ -8333,28 +8333,28 @@
         <v>2.061</v>
       </c>
       <c r="M86">
-        <v>0.9436190400000001</v>
+        <v>0.9548526000000001</v>
       </c>
       <c r="N86">
-        <v>1.11738096</v>
+        <v>1.1061474</v>
       </c>
       <c r="O86">
-        <v>0.335214288</v>
+        <v>0.3318442200000001</v>
       </c>
       <c r="P86">
-        <v>0.7821666720000002</v>
+        <v>0.7743031800000002</v>
       </c>
       <c r="Q86">
-        <v>0.9411666720000003</v>
+        <v>0.9333031800000002</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.7111259692255033</v>
+        <v>0.7526347195336897</v>
       </c>
       <c r="T86">
-        <v>4.63894710067215</v>
+        <v>4.928364477719431</v>
       </c>
       <c r="U86">
         <v>0.07580000000000001</v>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.18414414359422</v>
+        <v>2.15844833014017</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.1579962079300535</v>
+        <v>0.1576418607840264</v>
       </c>
       <c r="C87">
-        <v>5.409212317122401</v>
+        <v>5.307986017167583</v>
       </c>
       <c r="D87">
-        <v>14.8262123171224</v>
+        <v>14.87318601716758</v>
       </c>
       <c r="E87">
-        <v>10.377</v>
+        <v>10.5252</v>
       </c>
       <c r="F87">
-        <v>12.597</v>
+        <v>12.7452</v>
       </c>
       <c r="G87">
         <v>3.18</v>
@@ -8415,28 +8415,28 @@
         <v>2.061</v>
       </c>
       <c r="M87">
-        <v>0.9548526000000001</v>
+        <v>0.9660861600000001</v>
       </c>
       <c r="N87">
-        <v>1.1061474</v>
+        <v>1.09491384</v>
       </c>
       <c r="O87">
-        <v>0.3318442200000001</v>
+        <v>0.3284741520000001</v>
       </c>
       <c r="P87">
-        <v>0.7743031800000002</v>
+        <v>0.7664396880000002</v>
       </c>
       <c r="Q87">
-        <v>0.9333031800000002</v>
+        <v>0.9254396880000002</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.7526347195336897</v>
+        <v>0.8000732913144742</v>
       </c>
       <c r="T87">
-        <v>4.928364477719431</v>
+        <v>5.259127194344897</v>
       </c>
       <c r="U87">
         <v>0.07580000000000001</v>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.15844833014017</v>
+        <v>2.133350093743192</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.1576418607840264</v>
+        <v>0.1572875136379994</v>
       </c>
       <c r="C88">
-        <v>5.307986017167583</v>
+        <v>5.207058315611921</v>
       </c>
       <c r="D88">
-        <v>14.87318601716758</v>
+        <v>14.92045831561192</v>
       </c>
       <c r="E88">
-        <v>10.5252</v>
+        <v>10.6734</v>
       </c>
       <c r="F88">
-        <v>12.7452</v>
+        <v>12.8934</v>
       </c>
       <c r="G88">
         <v>3.18</v>
@@ -8497,28 +8497,28 @@
         <v>2.061</v>
       </c>
       <c r="M88">
-        <v>0.9660861600000001</v>
+        <v>0.9773197200000001</v>
       </c>
       <c r="N88">
-        <v>1.09491384</v>
+        <v>1.08368028</v>
       </c>
       <c r="O88">
-        <v>0.3284741520000001</v>
+        <v>0.3251040840000001</v>
       </c>
       <c r="P88">
-        <v>0.7664396880000002</v>
+        <v>0.7585761960000001</v>
       </c>
       <c r="Q88">
-        <v>0.9254396880000002</v>
+        <v>0.9175761960000002</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.8000732913144742</v>
+        <v>0.8548101049076873</v>
       </c>
       <c r="T88">
-        <v>5.259127194344897</v>
+        <v>5.640776482758896</v>
       </c>
       <c r="U88">
         <v>0.07580000000000001</v>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.133350093743192</v>
+        <v>2.108828828297868</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.1572875136379994</v>
+        <v>0.1569331664919723</v>
       </c>
       <c r="C89">
-        <v>5.207058315611921</v>
+        <v>5.10643206869071</v>
       </c>
       <c r="D89">
-        <v>14.92045831561192</v>
+        <v>14.96803206869071</v>
       </c>
       <c r="E89">
-        <v>10.6734</v>
+        <v>10.8216</v>
       </c>
       <c r="F89">
-        <v>12.8934</v>
+        <v>13.0416</v>
       </c>
       <c r="G89">
         <v>3.18</v>
@@ -8579,28 +8579,28 @@
         <v>2.061</v>
       </c>
       <c r="M89">
-        <v>0.9773197200000001</v>
+        <v>0.9885532800000001</v>
       </c>
       <c r="N89">
-        <v>1.08368028</v>
+        <v>1.07244672</v>
       </c>
       <c r="O89">
-        <v>0.3251040840000001</v>
+        <v>0.3217340160000001</v>
       </c>
       <c r="P89">
-        <v>0.7585761960000001</v>
+        <v>0.7507127040000002</v>
       </c>
       <c r="Q89">
-        <v>0.9175761960000002</v>
+        <v>0.9097127040000003</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8548101049076873</v>
+        <v>0.9186697207664358</v>
       </c>
       <c r="T89">
-        <v>5.640776482758896</v>
+        <v>6.086033985908561</v>
       </c>
       <c r="U89">
         <v>0.07580000000000001</v>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.108828828297868</v>
+        <v>2.084864864339937</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.1569331664919723</v>
+        <v>0.1565788193459452</v>
       </c>
       <c r="C90">
-        <v>5.10643206869071</v>
+        <v>5.006110169184078</v>
       </c>
       <c r="D90">
-        <v>14.96803206869071</v>
+        <v>15.01591016918408</v>
       </c>
       <c r="E90">
-        <v>10.8216</v>
+        <v>10.9698</v>
       </c>
       <c r="F90">
-        <v>13.0416</v>
+        <v>13.1898</v>
       </c>
       <c r="G90">
         <v>3.18</v>
@@ -8661,28 +8661,28 @@
         <v>2.061</v>
       </c>
       <c r="M90">
-        <v>0.9885532800000001</v>
+        <v>0.9997868400000001</v>
       </c>
       <c r="N90">
-        <v>1.07244672</v>
+        <v>1.06121316</v>
       </c>
       <c r="O90">
-        <v>0.3217340160000001</v>
+        <v>0.3183639480000001</v>
       </c>
       <c r="P90">
-        <v>0.7507127040000002</v>
+        <v>0.7428492120000003</v>
       </c>
       <c r="Q90">
-        <v>0.9097127040000003</v>
+        <v>0.9018492120000003</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.9186697207664358</v>
+        <v>0.9941401758722295</v>
       </c>
       <c r="T90">
-        <v>6.086033985908561</v>
+        <v>6.612247398721801</v>
       </c>
       <c r="U90">
         <v>0.07580000000000001</v>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.084864864339937</v>
+        <v>2.061439416426006</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.1565788193459452</v>
+        <v>0.1562244721999182</v>
       </c>
       <c r="C91">
-        <v>5.006110169184078</v>
+        <v>4.906095547003371</v>
       </c>
       <c r="D91">
-        <v>15.01591016918408</v>
+        <v>15.06409554700337</v>
       </c>
       <c r="E91">
-        <v>10.9698</v>
+        <v>11.118</v>
       </c>
       <c r="F91">
-        <v>13.1898</v>
+        <v>13.338</v>
       </c>
       <c r="G91">
         <v>3.18</v>
@@ -8743,28 +8743,28 @@
         <v>2.061</v>
       </c>
       <c r="M91">
-        <v>0.9997868400000001</v>
+        <v>1.0110204</v>
       </c>
       <c r="N91">
-        <v>1.06121316</v>
+        <v>1.0499796</v>
       </c>
       <c r="O91">
-        <v>0.3183639480000001</v>
+        <v>0.31499388</v>
       </c>
       <c r="P91">
-        <v>0.7428492120000003</v>
+        <v>0.7349857200000001</v>
       </c>
       <c r="Q91">
-        <v>0.9018492120000003</v>
+        <v>0.8939857200000001</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9941401758722295</v>
+        <v>1.084704721999182</v>
       </c>
       <c r="T91">
-        <v>6.612247398721801</v>
+        <v>7.24370349409769</v>
       </c>
       <c r="U91">
         <v>0.07580000000000001</v>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>2.061439416426006</v>
+        <v>2.038534534021272</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.1562244721999182</v>
+        <v>0.1558701250538911</v>
       </c>
       <c r="C92">
-        <v>4.906095547003371</v>
+        <v>4.80639116978881</v>
       </c>
       <c r="D92">
-        <v>15.06409554700337</v>
+        <v>15.11259116978881</v>
       </c>
       <c r="E92">
-        <v>11.118</v>
+        <v>11.2662</v>
       </c>
       <c r="F92">
-        <v>13.338</v>
+        <v>13.4862</v>
       </c>
       <c r="G92">
         <v>3.18</v>
@@ -8825,28 +8825,28 @@
         <v>2.061</v>
       </c>
       <c r="M92">
-        <v>1.0110204</v>
+        <v>1.02225396</v>
       </c>
       <c r="N92">
-        <v>1.0499796</v>
+        <v>1.03874604</v>
       </c>
       <c r="O92">
-        <v>0.31499388</v>
+        <v>0.3116238120000001</v>
       </c>
       <c r="P92">
-        <v>0.7349857200000001</v>
+        <v>0.7271222280000003</v>
       </c>
       <c r="Q92">
-        <v>0.8939857200000001</v>
+        <v>0.8861222280000003</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.084704721999182</v>
+        <v>1.195394722821013</v>
       </c>
       <c r="T92">
-        <v>7.24370349409769</v>
+        <v>8.015483166223776</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.038534534021272</v>
+        <v>2.016133055625434</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.1558701250538911</v>
+        <v>0.1646605779078641</v>
       </c>
       <c r="C93">
-        <v>4.80639116978881</v>
+        <v>3.540524383056761</v>
       </c>
       <c r="D93">
-        <v>15.11259116978881</v>
+        <v>13.99492438305676</v>
       </c>
       <c r="E93">
-        <v>11.2662</v>
+        <v>11.4144</v>
       </c>
       <c r="F93">
-        <v>13.4862</v>
+        <v>13.6344</v>
       </c>
       <c r="G93">
         <v>3.18</v>
@@ -8907,45 +8907,45 @@
         <v>2.061</v>
       </c>
       <c r="M93">
-        <v>1.02225396</v>
+        <v>1.227096</v>
       </c>
       <c r="N93">
-        <v>1.03874604</v>
+        <v>0.8339040000000004</v>
       </c>
       <c r="O93">
-        <v>0.3116238120000001</v>
+        <v>0.2501712000000001</v>
       </c>
       <c r="P93">
-        <v>0.7271222280000003</v>
+        <v>0.5837328000000004</v>
       </c>
       <c r="Q93">
-        <v>0.8861222280000003</v>
+        <v>0.7427328000000004</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.195394722821013</v>
+        <v>1.333757223848301</v>
       </c>
       <c r="T93">
-        <v>8.015483166223776</v>
+        <v>8.980207756381386</v>
       </c>
       <c r="U93">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V93">
         <v>0.3</v>
       </c>
       <c r="W93">
-        <v>0.05306</v>
+        <v>0.063</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y93">
-        <v>2.016133055625434</v>
+        <v>1.679575192161005</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.1646605779078641</v>
+        <v>0.164405630761837</v>
       </c>
       <c r="C94">
-        <v>3.540524383056761</v>
+        <v>3.422406985437503</v>
       </c>
       <c r="D94">
-        <v>13.99492438305676</v>
+        <v>14.0250069854375</v>
       </c>
       <c r="E94">
-        <v>11.4144</v>
+        <v>11.5626</v>
       </c>
       <c r="F94">
-        <v>13.6344</v>
+        <v>13.7826</v>
       </c>
       <c r="G94">
         <v>3.18</v>
@@ -8989,28 +8989,28 @@
         <v>2.061</v>
       </c>
       <c r="M94">
-        <v>1.227096</v>
+        <v>1.240434</v>
       </c>
       <c r="N94">
-        <v>0.8339040000000004</v>
+        <v>0.8205660000000004</v>
       </c>
       <c r="O94">
-        <v>0.2501712000000001</v>
+        <v>0.2461698000000001</v>
       </c>
       <c r="P94">
-        <v>0.5837328000000004</v>
+        <v>0.5743962000000002</v>
       </c>
       <c r="Q94">
-        <v>0.7427328000000004</v>
+        <v>0.7333962000000003</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.333757223848301</v>
+        <v>1.511651868026244</v>
       </c>
       <c r="T94">
-        <v>8.980207756381386</v>
+        <v>10.22056794372688</v>
       </c>
       <c r="U94">
         <v>0.09</v>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>1.679575192161005</v>
+        <v>1.661515243858198</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.164405630761837</v>
+        <v>0.1641506836158099</v>
       </c>
       <c r="C95">
-        <v>3.422406985437503</v>
+        <v>3.304419193721436</v>
       </c>
       <c r="D95">
-        <v>14.0250069854375</v>
+        <v>14.05521919372144</v>
       </c>
       <c r="E95">
-        <v>11.5626</v>
+        <v>11.7108</v>
       </c>
       <c r="F95">
-        <v>13.7826</v>
+        <v>13.9308</v>
       </c>
       <c r="G95">
         <v>3.18</v>
@@ -9071,28 +9071,28 @@
         <v>2.061</v>
       </c>
       <c r="M95">
-        <v>1.240434</v>
+        <v>1.253772</v>
       </c>
       <c r="N95">
-        <v>0.8205660000000004</v>
+        <v>0.8072280000000003</v>
       </c>
       <c r="O95">
-        <v>0.2461698000000001</v>
+        <v>0.2421684000000001</v>
       </c>
       <c r="P95">
-        <v>0.5743962000000002</v>
+        <v>0.5650596000000002</v>
       </c>
       <c r="Q95">
-        <v>0.7333962000000003</v>
+        <v>0.7240596000000002</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.511651868026244</v>
+        <v>1.748844726930167</v>
       </c>
       <c r="T95">
-        <v>10.22056794372688</v>
+        <v>11.87438152685421</v>
       </c>
       <c r="U95">
         <v>0.09</v>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>1.661515243858198</v>
+        <v>1.6438395497746</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.1641506836158099</v>
+        <v>0.1638957364697829</v>
       </c>
       <c r="C96">
-        <v>3.304419193721436</v>
+        <v>3.186561847295057</v>
       </c>
       <c r="D96">
-        <v>14.05521919372144</v>
+        <v>14.08556184729506</v>
       </c>
       <c r="E96">
-        <v>11.7108</v>
+        <v>11.859</v>
       </c>
       <c r="F96">
-        <v>13.9308</v>
+        <v>14.079</v>
       </c>
       <c r="G96">
         <v>3.18</v>
@@ -9153,28 +9153,28 @@
         <v>2.061</v>
       </c>
       <c r="M96">
-        <v>1.253772</v>
+        <v>1.26711</v>
       </c>
       <c r="N96">
-        <v>0.8072280000000003</v>
+        <v>0.7938900000000004</v>
       </c>
       <c r="O96">
-        <v>0.2421684000000001</v>
+        <v>0.2381670000000001</v>
       </c>
       <c r="P96">
-        <v>0.5650596000000002</v>
+        <v>0.5557230000000003</v>
       </c>
       <c r="Q96">
-        <v>0.7240596000000002</v>
+        <v>0.7147230000000003</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.748844726930167</v>
+        <v>2.08091472939566</v>
       </c>
       <c r="T96">
-        <v>11.87438152685421</v>
+        <v>14.18972054323248</v>
       </c>
       <c r="U96">
         <v>0.09</v>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>1.6438395497746</v>
+        <v>1.626535975566447</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.1638957364697829</v>
+        <v>0.1636407893237558</v>
       </c>
       <c r="C97">
-        <v>3.186561847295057</v>
+        <v>3.068835792808857</v>
       </c>
       <c r="D97">
-        <v>14.08556184729506</v>
+        <v>14.11603579280886</v>
       </c>
       <c r="E97">
-        <v>11.859</v>
+        <v>12.0072</v>
       </c>
       <c r="F97">
-        <v>14.079</v>
+        <v>14.2272</v>
       </c>
       <c r="G97">
         <v>3.18</v>
@@ -9235,28 +9235,28 @@
         <v>2.061</v>
       </c>
       <c r="M97">
-        <v>1.26711</v>
+        <v>1.280448</v>
       </c>
       <c r="N97">
-        <v>0.7938900000000004</v>
+        <v>0.7805520000000004</v>
       </c>
       <c r="O97">
-        <v>0.2381670000000001</v>
+        <v>0.2341656000000001</v>
       </c>
       <c r="P97">
-        <v>0.5557230000000003</v>
+        <v>0.5463864000000003</v>
       </c>
       <c r="Q97">
-        <v>0.7147230000000003</v>
+        <v>0.7053864000000003</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.08091472939566</v>
+        <v>2.5790197330939</v>
       </c>
       <c r="T97">
-        <v>14.18972054323248</v>
+        <v>17.66272906779988</v>
       </c>
       <c r="U97">
         <v>0.09</v>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>1.626535975566447</v>
+        <v>1.60959289248763</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.1636407893237558</v>
+        <v>0.1633858421777288</v>
       </c>
       <c r="C98">
-        <v>3.068835792808862</v>
+        <v>2.951241884256095</v>
       </c>
       <c r="D98">
-        <v>14.11603579280886</v>
+        <v>14.14664188425609</v>
       </c>
       <c r="E98">
-        <v>12.0072</v>
+        <v>12.1554</v>
       </c>
       <c r="F98">
-        <v>14.2272</v>
+        <v>14.3754</v>
       </c>
       <c r="G98">
         <v>3.18</v>
@@ -9317,28 +9317,28 @@
         <v>2.061</v>
       </c>
       <c r="M98">
-        <v>1.280448</v>
+        <v>1.293786</v>
       </c>
       <c r="N98">
-        <v>0.7805520000000004</v>
+        <v>0.7672140000000005</v>
       </c>
       <c r="O98">
-        <v>0.2341656000000001</v>
+        <v>0.2301642000000002</v>
       </c>
       <c r="P98">
-        <v>0.5463864000000003</v>
+        <v>0.5370498000000004</v>
       </c>
       <c r="Q98">
-        <v>0.7053864000000003</v>
+        <v>0.6960498000000004</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.579019733093892</v>
+        <v>3.409194739257623</v>
       </c>
       <c r="T98">
-        <v>17.66272906779983</v>
+        <v>23.45107660874547</v>
       </c>
       <c r="U98">
         <v>0.09</v>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>1.60959289248763</v>
+        <v>1.592999151327964</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.1633858421777288</v>
+        <v>0.1631308950317017</v>
       </c>
       <c r="C99">
-        <v>2.951241884256095</v>
+        <v>2.833780983052568</v>
       </c>
       <c r="D99">
-        <v>14.14664188425609</v>
+        <v>14.17738098305257</v>
       </c>
       <c r="E99">
-        <v>12.1554</v>
+        <v>12.3036</v>
       </c>
       <c r="F99">
-        <v>14.3754</v>
+        <v>14.5236</v>
       </c>
       <c r="G99">
         <v>3.18</v>
@@ -9399,28 +9399,28 @@
         <v>2.061</v>
       </c>
       <c r="M99">
-        <v>1.293786</v>
+        <v>1.307124</v>
       </c>
       <c r="N99">
-        <v>0.7672140000000005</v>
+        <v>0.7538760000000004</v>
       </c>
       <c r="O99">
-        <v>0.2301642000000002</v>
+        <v>0.2261628000000001</v>
       </c>
       <c r="P99">
-        <v>0.5370498000000004</v>
+        <v>0.5277132000000003</v>
       </c>
       <c r="Q99">
-        <v>0.6960498000000004</v>
+        <v>0.6867132000000004</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.409194739257623</v>
+        <v>5.06954475158508</v>
       </c>
       <c r="T99">
-        <v>23.45107660874547</v>
+        <v>35.02777169063674</v>
       </c>
       <c r="U99">
         <v>0.09</v>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>1.592999151327964</v>
+        <v>1.576744057947066</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.1631308950317017</v>
+        <v>0.1628759478856746</v>
       </c>
       <c r="C100">
-        <v>2.833780983052568</v>
+        <v>2.716453958117418</v>
       </c>
       <c r="D100">
-        <v>14.17738098305257</v>
+        <v>14.20825395811742</v>
       </c>
       <c r="E100">
-        <v>12.3036</v>
+        <v>12.4518</v>
       </c>
       <c r="F100">
-        <v>14.5236</v>
+        <v>14.6718</v>
       </c>
       <c r="G100">
         <v>3.18</v>
@@ -9481,28 +9481,28 @@
         <v>2.061</v>
       </c>
       <c r="M100">
-        <v>1.307124</v>
+        <v>1.320462</v>
       </c>
       <c r="N100">
-        <v>0.7538760000000004</v>
+        <v>0.7405380000000006</v>
       </c>
       <c r="O100">
-        <v>0.2261628000000001</v>
+        <v>0.2221614000000002</v>
       </c>
       <c r="P100">
-        <v>0.5277132000000003</v>
+        <v>0.5183766000000004</v>
       </c>
       <c r="Q100">
-        <v>0.6867132000000004</v>
+        <v>0.6773766000000004</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.06954475158508</v>
+        <v>10.05059478856745</v>
       </c>
       <c r="T100">
-        <v>35.02777169063674</v>
+        <v>69.75785693631056</v>
       </c>
       <c r="U100">
         <v>0.09</v>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>1.576744057947066</v>
+        <v>1.560817350291035</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.1628759478856746</v>
-      </c>
-      <c r="C101">
-        <v>2.716453958117418</v>
-      </c>
-      <c r="D101">
-        <v>14.20825395811742</v>
-      </c>
-      <c r="E101">
-        <v>12.4518</v>
-      </c>
-      <c r="F101">
-        <v>14.6718</v>
-      </c>
-      <c r="G101">
-        <v>3.18</v>
-      </c>
-      <c r="H101">
-        <v>12.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>2.22</v>
-      </c>
-      <c r="K101">
-        <v>0.159</v>
-      </c>
-      <c r="L101">
-        <v>2.061</v>
-      </c>
-      <c r="M101">
-        <v>1.320462</v>
-      </c>
-      <c r="N101">
-        <v>0.7405380000000006</v>
-      </c>
-      <c r="O101">
-        <v>0.2221614000000002</v>
-      </c>
-      <c r="P101">
-        <v>0.5183766000000004</v>
-      </c>
-      <c r="Q101">
-        <v>0.6773766000000004</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.05059478856745</v>
-      </c>
-      <c r="T101">
-        <v>69.75785693631056</v>
-      </c>
-      <c r="U101">
-        <v>0.09</v>
-      </c>
-      <c r="V101">
-        <v>0.3</v>
-      </c>
-      <c r="W101">
-        <v>0.063</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B3/B-</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>1.560817350291035</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
